--- a/www/data-entry-template/GLATAR_data_entry_template_v20_long.xlsx
+++ b/www/data-entry-template/GLATAR_data_entry_template_v20_long.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benhlina/Library/CloudStorage/Dropbox/GitHub/GLATAR-App/www/data-entry-template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CEEB1A3-ED16-594C-955A-5D63ACD80E21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28E787EC-E7F0-DC42-99F9-0631B339ADB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="34560" windowHeight="19000" xr2:uid="{DE6F8925-643B-304C-8933-23D4A9123DA3}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <sheet name="tbl_samples" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data_dictionary!$A$4:$D$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data_dictionary!$A$4:$D$75</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +47,7 @@
     <author>Ben Hlina</author>
   </authors>
   <commentList>
-    <comment ref="AI5" authorId="0" shapeId="0" xr:uid="{B4D33EEE-BEDB-B341-9363-9D1C96784118}">
+    <comment ref="AJ5" authorId="0" shapeId="0" xr:uid="{B4D33EEE-BEDB-B341-9363-9D1C96784118}">
       <text>
         <r>
           <rPr>
@@ -81,7 +81,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AJ5" authorId="0" shapeId="0" xr:uid="{238ED598-C074-2B4E-A8CF-63B7194C3AEA}">
+    <comment ref="AK5" authorId="0" shapeId="0" xr:uid="{238ED598-C074-2B4E-A8CF-63B7194C3AEA}">
       <text>
         <r>
           <rPr>
@@ -118,7 +118,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="328">
   <si>
     <t>Field Name</t>
   </si>
@@ -1196,6 +1196,18 @@
   <si>
     <t>Convert using the following: Kcal/g - multiple by 4184, Kcal/kg - multiple by 4.184, or Kjoules/g - multiple by 1000</t>
   </si>
+  <si>
+    <t>organism_type</t>
+  </si>
+  <si>
+    <t>as in: Invertebrate; format: character</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The organsim type </t>
+  </si>
+  <si>
+    <t>Algae, Amphibian, Fish, Invertebrate, or  Reptile</t>
+  </si>
 </sst>
 </file>
 
@@ -1535,6 +1547,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1542,7 +1555,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1884,7 +1896,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCDB0B4B-8041-E244-B061-95D35DE0CD3B}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F91"/>
+  <dimension ref="A1:F92"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" style="1" customWidth="1"/>
@@ -1897,20 +1909,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="49" t="s">
         <v>238</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
     </row>
     <row r="2" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="48" t="s">
+      <c r="A2" s="49" t="s">
         <v>162</v>
       </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="21" t="s">
@@ -1925,10 +1937,10 @@
       <c r="D4" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="51" t="s">
+      <c r="E4" s="48" t="s">
         <v>239</v>
       </c>
-      <c r="F4" s="51" t="s">
+      <c r="F4" s="48" t="s">
         <v>240</v>
       </c>
     </row>
@@ -2388,240 +2400,242 @@
       <c r="E32" s="30"/>
       <c r="F32" s="30"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" ht="28" x14ac:dyDescent="0.2">
       <c r="A33" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="B33" s="30" t="s">
-        <v>7</v>
+      <c r="B33" s="32" t="s">
+        <v>324</v>
       </c>
       <c r="C33" s="30" t="s">
-        <v>264</v>
+        <v>325</v>
       </c>
       <c r="D33" s="30" t="s">
-        <v>265</v>
-      </c>
-      <c r="E33" s="30" t="s">
-        <v>245</v>
+        <v>326</v>
+      </c>
+      <c r="E33" s="33" t="s">
+        <v>327</v>
       </c>
       <c r="F33" s="30"/>
     </row>
-    <row r="34" spans="1:6" ht="28" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" s="30" t="s">
         <v>119</v>
       </c>
       <c r="B34" s="30" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C34" s="30" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D34" s="30" t="s">
-        <v>179</v>
-      </c>
-      <c r="E34" s="33" t="s">
-        <v>246</v>
+        <v>265</v>
+      </c>
+      <c r="E34" s="30" t="s">
+        <v>245</v>
       </c>
       <c r="F34" s="30"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" ht="28" x14ac:dyDescent="0.2">
       <c r="A35" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="B35" s="32" t="s">
-        <v>13</v>
+      <c r="B35" s="30" t="s">
+        <v>8</v>
       </c>
       <c r="C35" s="30" t="s">
-        <v>47</v>
-      </c>
-      <c r="D35" s="33" t="s">
-        <v>109</v>
-      </c>
-      <c r="E35" s="30" t="s">
-        <v>247</v>
+        <v>266</v>
+      </c>
+      <c r="D35" s="30" t="s">
+        <v>179</v>
+      </c>
+      <c r="E35" s="33" t="s">
+        <v>246</v>
       </c>
       <c r="F35" s="30"/>
     </row>
-    <row r="36" spans="1:6" ht="28" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="B36" s="30" t="s">
-        <v>156</v>
+      <c r="B36" s="32" t="s">
+        <v>13</v>
       </c>
       <c r="C36" s="30" t="s">
-        <v>267</v>
+        <v>47</v>
       </c>
       <c r="D36" s="33" t="s">
-        <v>268</v>
-      </c>
-      <c r="E36" s="30"/>
+        <v>109</v>
+      </c>
+      <c r="E36" s="30" t="s">
+        <v>247</v>
+      </c>
       <c r="F36" s="30"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" ht="28" x14ac:dyDescent="0.2">
       <c r="A37" s="30" t="s">
         <v>119</v>
       </c>
       <c r="B37" s="30" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="C37" s="30" t="s">
-        <v>287</v>
-      </c>
-      <c r="D37" s="30" t="s">
-        <v>40</v>
+        <v>267</v>
+      </c>
+      <c r="D37" s="33" t="s">
+        <v>268</v>
       </c>
       <c r="E37" s="30"/>
       <c r="F37" s="30"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" s="30" t="s">
-        <v>155</v>
+        <v>119</v>
       </c>
       <c r="B38" s="30" t="s">
-        <v>96</v>
+        <v>170</v>
       </c>
       <c r="C38" s="30" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D38" s="30" t="s">
-        <v>180</v>
+        <v>40</v>
       </c>
       <c r="E38" s="30"/>
       <c r="F38" s="30"/>
     </row>
-    <row r="39" spans="1:6" ht="28" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" s="30" t="s">
         <v>155</v>
       </c>
       <c r="B39" s="30" t="s">
+        <v>96</v>
+      </c>
+      <c r="C39" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="D39" s="30" t="s">
+        <v>180</v>
+      </c>
+      <c r="E39" s="30"/>
+      <c r="F39" s="30"/>
+    </row>
+    <row r="40" spans="1:6" ht="28" x14ac:dyDescent="0.2">
+      <c r="A40" s="30" t="s">
+        <v>155</v>
+      </c>
+      <c r="B40" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="C39" s="30" t="s">
+      <c r="C40" s="30" t="s">
         <v>269</v>
       </c>
-      <c r="D39" s="33" t="s">
+      <c r="D40" s="33" t="s">
         <v>270</v>
       </c>
-      <c r="E39" s="30" t="s">
+      <c r="E40" s="30" t="s">
         <v>248</v>
       </c>
-      <c r="F39" s="30"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A40" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="B40" s="30" t="s">
-        <v>171</v>
-      </c>
-      <c r="C40" s="30" t="s">
-        <v>289</v>
-      </c>
-      <c r="D40" s="30" t="s">
-        <v>271</v>
-      </c>
-      <c r="E40" s="30"/>
       <c r="F40" s="30"/>
     </row>
-    <row r="41" spans="1:6" ht="42" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" s="30" t="s">
         <v>119</v>
       </c>
       <c r="B41" s="30" t="s">
-        <v>231</v>
+        <v>171</v>
       </c>
       <c r="C41" s="30" t="s">
-        <v>233</v>
-      </c>
-      <c r="D41" s="33" t="s">
-        <v>272</v>
-      </c>
-      <c r="E41" s="33" t="s">
-        <v>286</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="D41" s="30" t="s">
+        <v>271</v>
+      </c>
+      <c r="E41" s="30"/>
       <c r="F41" s="30"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" ht="42" x14ac:dyDescent="0.2">
       <c r="A42" s="30" t="s">
         <v>119</v>
       </c>
       <c r="B42" s="30" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C42" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="D42" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="E42" s="30"/>
+        <v>233</v>
+      </c>
+      <c r="D42" s="33" t="s">
+        <v>272</v>
+      </c>
+      <c r="E42" s="33" t="s">
+        <v>286</v>
+      </c>
       <c r="F42" s="30"/>
     </row>
-    <row r="43" spans="1:6" ht="84" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="B43" s="32" t="s">
-        <v>9</v>
+      <c r="B43" s="30" t="s">
+        <v>232</v>
       </c>
       <c r="C43" s="30" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D43" s="30" t="s">
-        <v>12</v>
-      </c>
-      <c r="E43" s="33" t="s">
-        <v>249</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="E43" s="30"/>
       <c r="F43" s="30"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6" ht="84" x14ac:dyDescent="0.2">
       <c r="A44" s="30" t="s">
         <v>119</v>
       </c>
       <c r="B44" s="32" t="s">
-        <v>62</v>
+        <v>9</v>
       </c>
       <c r="C44" s="30" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D44" s="30" t="s">
-        <v>273</v>
-      </c>
-      <c r="E44" s="30" t="s">
-        <v>250</v>
+        <v>12</v>
+      </c>
+      <c r="E44" s="33" t="s">
+        <v>249</v>
       </c>
       <c r="F44" s="30"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="B45" s="30" t="s">
-        <v>102</v>
+        <v>119</v>
+      </c>
+      <c r="B45" s="32" t="s">
+        <v>62</v>
       </c>
       <c r="C45" s="30" t="s">
-        <v>104</v>
+        <v>63</v>
       </c>
       <c r="D45" s="30" t="s">
-        <v>105</v>
-      </c>
-      <c r="E45" s="30"/>
+        <v>273</v>
+      </c>
+      <c r="E45" s="30" t="s">
+        <v>250</v>
+      </c>
       <c r="F45" s="30"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="B46" s="32" t="s">
-        <v>17</v>
+      <c r="B46" s="30" t="s">
+        <v>102</v>
       </c>
       <c r="C46" s="30" t="s">
-        <v>48</v>
+        <v>104</v>
       </c>
       <c r="D46" s="30" t="s">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="E46" s="30"/>
       <c r="F46" s="30"/>
@@ -2630,14 +2644,14 @@
       <c r="A47" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="B47" s="30" t="s">
-        <v>19</v>
+      <c r="B47" s="32" t="s">
+        <v>17</v>
       </c>
       <c r="C47" s="30" t="s">
-        <v>154</v>
+        <v>48</v>
       </c>
       <c r="D47" s="30" t="s">
-        <v>274</v>
+        <v>26</v>
       </c>
       <c r="E47" s="30"/>
       <c r="F47" s="30"/>
@@ -2647,13 +2661,13 @@
         <v>16</v>
       </c>
       <c r="B48" s="30" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C48" s="30" t="s">
-        <v>52</v>
+        <v>154</v>
       </c>
       <c r="D48" s="30" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E48" s="30"/>
       <c r="F48" s="30"/>
@@ -2663,99 +2677,99 @@
         <v>16</v>
       </c>
       <c r="B49" s="30" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C49" s="30" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="D49" s="30" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E49" s="30"/>
       <c r="F49" s="30"/>
     </row>
-    <row r="50" spans="1:6" ht="70" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" s="30" t="s">
         <v>16</v>
       </c>
       <c r="B50" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>277</v>
+        <v>21</v>
+      </c>
+      <c r="C50" s="30" t="s">
+        <v>138</v>
+      </c>
+      <c r="D50" s="30" t="s">
+        <v>276</v>
       </c>
       <c r="E50" s="30"/>
-      <c r="F50" s="33" t="s">
-        <v>251</v>
-      </c>
+      <c r="F50" s="30"/>
     </row>
     <row r="51" spans="1:6" ht="70" x14ac:dyDescent="0.2">
       <c r="A51" s="30" t="s">
         <v>16</v>
       </c>
       <c r="B51" s="30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E51" s="30"/>
       <c r="F51" s="33" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="70" x14ac:dyDescent="0.2">
       <c r="A52" s="30" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B52" s="30" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>279</v>
+        <v>152</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E52" s="33" t="s">
-        <v>253</v>
-      </c>
-      <c r="F52" s="30"/>
-    </row>
-    <row r="53" spans="1:6" ht="28" x14ac:dyDescent="0.2">
+        <v>278</v>
+      </c>
+      <c r="E52" s="30"/>
+      <c r="F52" s="33" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="70" x14ac:dyDescent="0.2">
       <c r="A53" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="B53" s="34" t="s">
-        <v>92</v>
+      <c r="B53" s="30" t="s">
+        <v>55</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="E53" s="30"/>
+        <v>56</v>
+      </c>
+      <c r="E53" s="33" t="s">
+        <v>253</v>
+      </c>
       <c r="F53" s="30"/>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:6" ht="28" x14ac:dyDescent="0.2">
       <c r="A54" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="B54" s="30" t="s">
-        <v>116</v>
-      </c>
-      <c r="C54" s="30" t="s">
-        <v>141</v>
-      </c>
-      <c r="D54" s="30" t="s">
-        <v>282</v>
+      <c r="B54" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>281</v>
       </c>
       <c r="E54" s="30"/>
       <c r="F54" s="30"/>
@@ -2765,101 +2779,101 @@
         <v>27</v>
       </c>
       <c r="B55" s="30" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="C55" s="30" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D55" s="30" t="s">
-        <v>100</v>
-      </c>
-      <c r="E55" s="30" t="s">
-        <v>254</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="E55" s="30"/>
       <c r="F55" s="30"/>
     </row>
-    <row r="56" spans="1:6" ht="42" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" s="30" t="s">
         <v>27</v>
       </c>
       <c r="B56" s="30" t="s">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="C56" s="30" t="s">
-        <v>290</v>
+        <v>142</v>
       </c>
       <c r="D56" s="30" t="s">
-        <v>182</v>
-      </c>
-      <c r="E56" s="30"/>
-      <c r="F56" s="33" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="56" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="E56" s="30" t="s">
+        <v>254</v>
+      </c>
+      <c r="F56" s="30"/>
+    </row>
+    <row r="57" spans="1:6" ht="42" x14ac:dyDescent="0.2">
       <c r="A57" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="B57" s="35" t="s">
-        <v>99</v>
+      <c r="B57" s="30" t="s">
+        <v>120</v>
       </c>
       <c r="C57" s="30" t="s">
-        <v>148</v>
+        <v>290</v>
       </c>
       <c r="D57" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="E57" s="30" t="s">
-        <v>255</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="E57" s="30"/>
       <c r="F57" s="33" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="56" x14ac:dyDescent="0.2">
       <c r="A58" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="B58" s="30" t="s">
-        <v>117</v>
+      <c r="B58" s="35" t="s">
+        <v>99</v>
       </c>
       <c r="C58" s="30" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="D58" s="30" t="s">
-        <v>123</v>
-      </c>
-      <c r="E58" s="30"/>
-      <c r="F58" s="30"/>
+        <v>101</v>
+      </c>
+      <c r="E58" s="30" t="s">
+        <v>255</v>
+      </c>
+      <c r="F58" s="33" t="s">
+        <v>323</v>
+      </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" s="30" t="s">
         <v>27</v>
       </c>
       <c r="B59" s="30" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C59" s="30" t="s">
-        <v>283</v>
+        <v>143</v>
       </c>
       <c r="D59" s="30" t="s">
-        <v>220</v>
+        <v>123</v>
       </c>
       <c r="E59" s="30"/>
       <c r="F59" s="30"/>
     </row>
-    <row r="60" spans="1:6" ht="28" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="B60" s="35" t="s">
-        <v>121</v>
+      <c r="B60" s="30" t="s">
+        <v>118</v>
       </c>
       <c r="C60" s="30" t="s">
-        <v>284</v>
-      </c>
-      <c r="D60" s="33" t="s">
-        <v>124</v>
+        <v>283</v>
+      </c>
+      <c r="D60" s="30" t="s">
+        <v>220</v>
       </c>
       <c r="E60" s="30"/>
       <c r="F60" s="30"/>
@@ -2869,29 +2883,29 @@
         <v>27</v>
       </c>
       <c r="B61" s="35" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C61" s="30" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D61" s="33" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E61" s="30"/>
       <c r="F61" s="30"/>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:6" ht="28" x14ac:dyDescent="0.2">
       <c r="A62" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="B62" s="30" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="B62" s="35" t="s">
+        <v>122</v>
       </c>
       <c r="C62" s="30" t="s">
-        <v>291</v>
-      </c>
-      <c r="D62" s="30" t="s">
-        <v>41</v>
+        <v>285</v>
+      </c>
+      <c r="D62" s="33" t="s">
+        <v>125</v>
       </c>
       <c r="E62" s="30"/>
       <c r="F62" s="30"/>
@@ -2901,13 +2915,13 @@
         <v>29</v>
       </c>
       <c r="B63" s="30" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C63" s="30" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D63" s="30" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E63" s="30"/>
       <c r="F63" s="30"/>
@@ -2917,13 +2931,13 @@
         <v>29</v>
       </c>
       <c r="B64" s="30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C64" s="30" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D64" s="30" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E64" s="30"/>
       <c r="F64" s="30"/>
@@ -2933,13 +2947,13 @@
         <v>29</v>
       </c>
       <c r="B65" s="30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C65" s="30" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D65" s="30" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E65" s="30"/>
       <c r="F65" s="30"/>
@@ -2949,13 +2963,13 @@
         <v>29</v>
       </c>
       <c r="B66" s="30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C66" s="30" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="D66" s="30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E66" s="30"/>
       <c r="F66" s="30"/>
@@ -2965,49 +2979,49 @@
         <v>29</v>
       </c>
       <c r="B67" s="30" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C67" s="30" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D67" s="30" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E67" s="30"/>
       <c r="F67" s="30"/>
     </row>
-    <row r="68" spans="1:6" ht="28" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68" s="30" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="B68" s="30" t="s">
-        <v>181</v>
+        <v>34</v>
       </c>
       <c r="C68" s="30" t="s">
-        <v>234</v>
-      </c>
-      <c r="D68" s="33" t="s">
-        <v>235</v>
-      </c>
-      <c r="E68" s="30" t="s">
-        <v>256</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="D68" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="E68" s="30"/>
       <c r="F68" s="30"/>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:6" ht="28" x14ac:dyDescent="0.2">
       <c r="A69" s="30" t="s">
         <v>38</v>
       </c>
       <c r="B69" s="30" t="s">
-        <v>35</v>
+        <v>181</v>
       </c>
       <c r="C69" s="30" t="s">
-        <v>296</v>
-      </c>
-      <c r="D69" s="30" t="s">
-        <v>49</v>
-      </c>
-      <c r="E69" s="30"/>
+        <v>234</v>
+      </c>
+      <c r="D69" s="33" t="s">
+        <v>235</v>
+      </c>
+      <c r="E69" s="30" t="s">
+        <v>256</v>
+      </c>
       <c r="F69" s="30"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.2">
@@ -3015,13 +3029,13 @@
         <v>38</v>
       </c>
       <c r="B70" s="30" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C70" s="30" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D70" s="30" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E70" s="30"/>
       <c r="F70" s="30"/>
@@ -3031,13 +3045,13 @@
         <v>38</v>
       </c>
       <c r="B71" s="30" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C71" s="30" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D71" s="30" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E71" s="30"/>
       <c r="F71" s="30"/>
@@ -3047,13 +3061,13 @@
         <v>38</v>
       </c>
       <c r="B72" s="30" t="s">
-        <v>183</v>
+        <v>37</v>
       </c>
       <c r="C72" s="30" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D72" s="30" t="s">
-        <v>184</v>
+        <v>51</v>
       </c>
       <c r="E72" s="30"/>
       <c r="F72" s="30"/>
@@ -3063,13 +3077,13 @@
         <v>38</v>
       </c>
       <c r="B73" s="30" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C73" s="30" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D73" s="30" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E73" s="30"/>
       <c r="F73" s="30"/>
@@ -3079,49 +3093,47 @@
         <v>38</v>
       </c>
       <c r="B74" s="30" t="s">
-        <v>126</v>
+        <v>186</v>
       </c>
       <c r="C74" s="30" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D74" s="30" t="s">
-        <v>127</v>
+        <v>185</v>
       </c>
       <c r="E74" s="30"/>
       <c r="F74" s="30"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75" s="30" t="s">
-        <v>187</v>
+        <v>38</v>
       </c>
       <c r="B75" s="30" t="s">
-        <v>188</v>
+        <v>126</v>
       </c>
       <c r="C75" s="30" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D75" s="30" t="s">
-        <v>189</v>
+        <v>127</v>
       </c>
       <c r="E75" s="30"/>
       <c r="F75" s="30"/>
     </row>
-    <row r="76" spans="1:6" ht="28" x14ac:dyDescent="0.2">
-      <c r="A76" s="33" t="s">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A76" s="30" t="s">
         <v>187</v>
       </c>
-      <c r="B76" s="33" t="s">
-        <v>190</v>
-      </c>
-      <c r="C76" s="33" t="s">
-        <v>191</v>
-      </c>
-      <c r="D76" s="33" t="s">
-        <v>192</v>
-      </c>
-      <c r="E76" s="30" t="s">
-        <v>312</v>
-      </c>
+      <c r="B76" s="30" t="s">
+        <v>188</v>
+      </c>
+      <c r="C76" s="30" t="s">
+        <v>302</v>
+      </c>
+      <c r="D76" s="30" t="s">
+        <v>189</v>
+      </c>
+      <c r="E76" s="30"/>
       <c r="F76" s="30"/>
     </row>
     <row r="77" spans="1:6" ht="28" x14ac:dyDescent="0.2">
@@ -3129,185 +3141,187 @@
         <v>187</v>
       </c>
       <c r="B77" s="33" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C77" s="33" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D77" s="33" t="s">
-        <v>195</v>
-      </c>
-      <c r="E77" s="33" t="s">
-        <v>313</v>
+        <v>192</v>
+      </c>
+      <c r="E77" s="30" t="s">
+        <v>312</v>
       </c>
       <c r="F77" s="30"/>
     </row>
     <row r="78" spans="1:6" ht="28" x14ac:dyDescent="0.2">
       <c r="A78" s="33" t="s">
-        <v>196</v>
-      </c>
-      <c r="B78" s="34" t="s">
-        <v>197</v>
+        <v>187</v>
+      </c>
+      <c r="B78" s="33" t="s">
+        <v>193</v>
       </c>
       <c r="C78" s="33" t="s">
-        <v>303</v>
+        <v>194</v>
       </c>
       <c r="D78" s="33" t="s">
-        <v>198</v>
-      </c>
-      <c r="E78" s="30"/>
+        <v>195</v>
+      </c>
+      <c r="E78" s="33" t="s">
+        <v>313</v>
+      </c>
       <c r="F78" s="30"/>
     </row>
-    <row r="79" spans="1:6" ht="42" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:6" ht="28" x14ac:dyDescent="0.2">
       <c r="A79" s="33" t="s">
         <v>196</v>
       </c>
       <c r="B79" s="34" t="s">
+        <v>197</v>
+      </c>
+      <c r="C79" s="33" t="s">
+        <v>303</v>
+      </c>
+      <c r="D79" s="33" t="s">
+        <v>198</v>
+      </c>
+      <c r="E79" s="30"/>
+      <c r="F79" s="30"/>
+    </row>
+    <row r="80" spans="1:6" ht="42" x14ac:dyDescent="0.2">
+      <c r="A80" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="B80" s="34" t="s">
         <v>199</v>
       </c>
-      <c r="C79" s="33" t="s">
+      <c r="C80" s="33" t="s">
         <v>306</v>
       </c>
-      <c r="D79" s="33" t="s">
+      <c r="D80" s="33" t="s">
         <v>307</v>
       </c>
-      <c r="E79" s="30" t="s">
+      <c r="E80" s="30" t="s">
         <v>314</v>
       </c>
-      <c r="F79" s="30"/>
-    </row>
-    <row r="80" spans="1:6" ht="112" x14ac:dyDescent="0.2">
-      <c r="A80" s="30" t="s">
+      <c r="F80" s="30"/>
+    </row>
+    <row r="81" spans="1:6" ht="112" x14ac:dyDescent="0.2">
+      <c r="A81" s="30" t="s">
         <v>196</v>
       </c>
-      <c r="B80" s="35" t="s">
+      <c r="B81" s="35" t="s">
         <v>200</v>
       </c>
-      <c r="C80" s="30" t="s">
+      <c r="C81" s="30" t="s">
         <v>201</v>
       </c>
-      <c r="D80" s="30" t="s">
+      <c r="D81" s="30" t="s">
         <v>202</v>
       </c>
-      <c r="E80" s="33" t="s">
+      <c r="E81" s="33" t="s">
         <v>315</v>
       </c>
-      <c r="F80" s="30"/>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A81" s="30" t="s">
-        <v>203</v>
-      </c>
-      <c r="B81" s="30" t="s">
-        <v>204</v>
-      </c>
-      <c r="C81" s="30" t="s">
-        <v>230</v>
-      </c>
-      <c r="D81" s="33" t="s">
-        <v>205</v>
-      </c>
-      <c r="E81" s="30"/>
       <c r="F81" s="30"/>
     </row>
-    <row r="82" spans="1:6" ht="42" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82" s="30" t="s">
         <v>203</v>
       </c>
       <c r="B82" s="30" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C82" s="30" t="s">
-        <v>306</v>
+        <v>230</v>
       </c>
       <c r="D82" s="33" t="s">
-        <v>308</v>
-      </c>
-      <c r="E82" s="30" t="s">
-        <v>317</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="E82" s="30"/>
       <c r="F82" s="30"/>
     </row>
-    <row r="83" spans="1:6" ht="84" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:6" ht="42" x14ac:dyDescent="0.2">
       <c r="A83" s="30" t="s">
         <v>203</v>
       </c>
       <c r="B83" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="C83" s="30" t="s">
+        <v>306</v>
+      </c>
+      <c r="D83" s="33" t="s">
+        <v>308</v>
+      </c>
+      <c r="E83" s="30" t="s">
+        <v>317</v>
+      </c>
+      <c r="F83" s="30"/>
+    </row>
+    <row r="84" spans="1:6" ht="84" x14ac:dyDescent="0.2">
+      <c r="A84" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="B84" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="C83" s="30" t="s">
+      <c r="C84" s="30" t="s">
         <v>227</v>
       </c>
-      <c r="D83" s="33" t="s">
+      <c r="D84" s="33" t="s">
         <v>208</v>
       </c>
-      <c r="E83" s="33" t="s">
+      <c r="E84" s="33" t="s">
         <v>316</v>
       </c>
-      <c r="F83" s="30"/>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A84" s="30" t="s">
-        <v>219</v>
-      </c>
-      <c r="B84" s="30" t="s">
-        <v>209</v>
-      </c>
-      <c r="C84" s="30" t="s">
-        <v>224</v>
-      </c>
-      <c r="D84" s="30" t="s">
-        <v>210</v>
-      </c>
-      <c r="E84" s="33"/>
       <c r="F84" s="30"/>
     </row>
-    <row r="85" spans="1:6" ht="42" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85" s="30" t="s">
         <v>219</v>
       </c>
-      <c r="B85" s="40" t="s">
-        <v>221</v>
+      <c r="B85" s="30" t="s">
+        <v>209</v>
       </c>
       <c r="C85" s="30" t="s">
-        <v>225</v>
-      </c>
-      <c r="D85" s="33" t="s">
-        <v>223</v>
-      </c>
-      <c r="E85" s="33" t="s">
-        <v>318</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="D85" s="30" t="s">
+        <v>210</v>
+      </c>
+      <c r="E85" s="33"/>
       <c r="F85" s="30"/>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:6" ht="42" x14ac:dyDescent="0.2">
       <c r="A86" s="30" t="s">
         <v>219</v>
       </c>
       <c r="B86" s="40" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C86" s="30" t="s">
-        <v>226</v>
-      </c>
-      <c r="D86" s="30" t="s">
-        <v>319</v>
-      </c>
-      <c r="E86" s="30"/>
+        <v>225</v>
+      </c>
+      <c r="D86" s="33" t="s">
+        <v>223</v>
+      </c>
+      <c r="E86" s="33" t="s">
+        <v>318</v>
+      </c>
       <c r="F86" s="30"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87" s="30" t="s">
-        <v>217</v>
-      </c>
-      <c r="B87" s="30" t="s">
-        <v>211</v>
+        <v>219</v>
+      </c>
+      <c r="B87" s="40" t="s">
+        <v>222</v>
       </c>
       <c r="C87" s="30" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D87" s="30" t="s">
-        <v>212</v>
+        <v>319</v>
       </c>
       <c r="E87" s="30"/>
       <c r="F87" s="30"/>
@@ -3317,17 +3331,15 @@
         <v>217</v>
       </c>
       <c r="B88" s="30" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C88" s="30" t="s">
-        <v>320</v>
+        <v>228</v>
       </c>
       <c r="D88" s="30" t="s">
-        <v>214</v>
-      </c>
-      <c r="E88" s="30" t="s">
-        <v>321</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="E88" s="30"/>
       <c r="F88" s="30"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.2">
@@ -3335,15 +3347,17 @@
         <v>217</v>
       </c>
       <c r="B89" s="30" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="C89" s="30" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="D89" s="30" t="s">
-        <v>309</v>
-      </c>
-      <c r="E89" s="30"/>
+        <v>214</v>
+      </c>
+      <c r="E89" s="30" t="s">
+        <v>321</v>
+      </c>
       <c r="F89" s="30"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.2">
@@ -3351,13 +3365,13 @@
         <v>217</v>
       </c>
       <c r="B90" s="30" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C90" s="30" t="s">
-        <v>229</v>
+        <v>304</v>
       </c>
       <c r="D90" s="30" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E90" s="30"/>
       <c r="F90" s="30"/>
@@ -3367,16 +3381,32 @@
         <v>217</v>
       </c>
       <c r="B91" s="30" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C91" s="30" t="s">
-        <v>305</v>
+        <v>229</v>
       </c>
       <c r="D91" s="30" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E91" s="30"/>
       <c r="F91" s="30"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A92" s="30" t="s">
+        <v>217</v>
+      </c>
+      <c r="B92" s="30" t="s">
+        <v>216</v>
+      </c>
+      <c r="C92" s="30" t="s">
+        <v>305</v>
+      </c>
+      <c r="D92" s="30" t="s">
+        <v>311</v>
+      </c>
+      <c r="E92" s="30"/>
+      <c r="F92" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3399,27 +3429,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="19" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="50" t="s">
         <v>172</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
       <c r="D1" s="10" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
       <c r="D2" s="11"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="49"/>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
+      <c r="A3" s="50"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="50"/>
       <c r="D3" s="11" t="s">
         <v>176</v>
       </c>
@@ -3465,27 +3495,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="19" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="50" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
       <c r="D1" s="10" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
       <c r="D2" s="11"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A3" s="49"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
+      <c r="A3" s="50"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="51"/>
       <c r="D3" s="11" t="s">
         <v>25</v>
       </c>
@@ -44443,7 +44473,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED99CF4A-5D49-794D-A1CB-3B08F37AF445}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:BR14"/>
+  <dimension ref="A1:BS14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20.5" customWidth="1"/>
@@ -44454,116 +44484,116 @@
     <col min="7" max="7" width="22.5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="26.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="13" customWidth="1"/>
-    <col min="12" max="12" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.1640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9" style="8" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.5" style="8" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="15.5" customWidth="1"/>
-    <col min="28" max="28" width="10.83203125" customWidth="1"/>
-    <col min="29" max="29" width="22.6640625" customWidth="1"/>
-    <col min="30" max="30" width="31.1640625" customWidth="1"/>
-    <col min="31" max="31" width="17.5" customWidth="1"/>
-    <col min="32" max="32" width="27" customWidth="1"/>
-    <col min="33" max="33" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="18.1640625" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="42" max="45" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="21.5" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="13" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="21.83203125" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="62" max="63" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="14.33203125" customWidth="1"/>
-    <col min="65" max="65" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="13" customWidth="1"/>
+    <col min="13" max="13" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9" style="8" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="15.5" customWidth="1"/>
+    <col min="29" max="29" width="10.83203125" customWidth="1"/>
+    <col min="30" max="30" width="22.6640625" customWidth="1"/>
+    <col min="31" max="31" width="31.1640625" customWidth="1"/>
+    <col min="32" max="32" width="17.5" customWidth="1"/>
+    <col min="33" max="33" width="27" customWidth="1"/>
+    <col min="34" max="34" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="43" max="46" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="21.5" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="13" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="21.83203125" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="63" max="64" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="14.33203125" customWidth="1"/>
+    <col min="66" max="66" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="16.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:70" ht="19" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
+    <row r="1" spans="1:71" ht="19" x14ac:dyDescent="0.25">
+      <c r="A1" s="50" t="s">
         <v>159</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
       <c r="D1" s="5" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="2" spans="1:70" x14ac:dyDescent="0.2">
-      <c r="A2" s="49" t="s">
+    <row r="2" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="A2" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
       <c r="D2" s="6"/>
     </row>
-    <row r="3" spans="1:70" x14ac:dyDescent="0.2">
-      <c r="A3" s="49"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
+    <row r="3" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="A3" s="50"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="51"/>
       <c r="D3" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:70" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>119</v>
       </c>
-      <c r="X4" t="s">
+      <c r="Y4" t="s">
         <v>16</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AF4" t="s">
         <v>27</v>
       </c>
-      <c r="AO4" t="s">
+      <c r="AP4" t="s">
         <v>29</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AV4" t="s">
         <v>38</v>
       </c>
-      <c r="BB4" s="37" t="s">
+      <c r="BC4" s="37" t="s">
         <v>187</v>
       </c>
-      <c r="BC4" s="37"/>
       <c r="BD4" s="37"/>
-      <c r="BE4" s="37" t="s">
+      <c r="BE4" s="37"/>
+      <c r="BF4" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="BF4" s="37"/>
       <c r="BG4" s="37"/>
-      <c r="BH4" s="37" t="s">
+      <c r="BH4" s="37"/>
+      <c r="BI4" s="37" t="s">
         <v>203</v>
       </c>
-      <c r="BI4" s="38"/>
       <c r="BJ4" s="38"/>
-      <c r="BK4" s="38" t="s">
+      <c r="BK4" s="38"/>
+      <c r="BL4" s="38" t="s">
         <v>219</v>
       </c>
-      <c r="BL4" s="38"/>
       <c r="BM4" s="38"/>
-      <c r="BN4" s="38" t="s">
+      <c r="BN4" s="38"/>
+      <c r="BO4" s="38" t="s">
         <v>217</v>
       </c>
-      <c r="BO4" s="38"/>
       <c r="BP4" s="38"/>
       <c r="BQ4" s="38"/>
       <c r="BR4" s="38"/>
-    </row>
-    <row r="5" spans="1:70" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="BS4" s="38"/>
+    </row>
+    <row r="5" spans="1:71" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="42" t="s">
         <v>14</v>
       </c>
@@ -44598,194 +44628,197 @@
         <v>103</v>
       </c>
       <c r="L5" s="36" t="s">
+        <v>324</v>
+      </c>
+      <c r="M5" s="36" t="s">
         <v>166</v>
       </c>
-      <c r="M5" s="36" t="s">
+      <c r="N5" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="N5" s="44" t="s">
+      <c r="O5" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="O5" s="36" t="s">
+      <c r="P5" s="36" t="s">
         <v>156</v>
       </c>
-      <c r="P5" s="36" t="s">
+      <c r="Q5" s="36" t="s">
         <v>170</v>
       </c>
-      <c r="Q5" s="36" t="s">
+      <c r="R5" s="36" t="s">
         <v>96</v>
       </c>
-      <c r="R5" s="36" t="s">
+      <c r="S5" s="36" t="s">
         <v>97</v>
       </c>
-      <c r="S5" s="36" t="s">
+      <c r="T5" s="36" t="s">
         <v>171</v>
       </c>
-      <c r="T5" s="46" t="s">
+      <c r="U5" s="46" t="s">
         <v>231</v>
       </c>
-      <c r="U5" s="45" t="s">
+      <c r="V5" s="45" t="s">
         <v>232</v>
       </c>
-      <c r="V5" s="44" t="s">
+      <c r="W5" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="W5" s="46" t="s">
+      <c r="X5" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="X5" s="45" t="s">
+      <c r="Y5" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="Y5" s="44" t="s">
+      <c r="Z5" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="Z5" s="36" t="s">
+      <c r="AA5" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="AA5" s="36" t="s">
+      <c r="AB5" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="AB5" s="36" t="s">
+      <c r="AC5" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="AC5" s="47" t="s">
+      <c r="AD5" s="47" t="s">
         <v>167</v>
       </c>
-      <c r="AD5" s="47" t="s">
+      <c r="AE5" s="47" t="s">
         <v>168</v>
       </c>
-      <c r="AE5" s="47" t="s">
+      <c r="AF5" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="AF5" s="47" t="s">
+      <c r="AG5" s="47" t="s">
         <v>92</v>
       </c>
-      <c r="AG5" s="36" t="s">
+      <c r="AH5" s="36" t="s">
         <v>116</v>
       </c>
-      <c r="AH5" s="36" t="s">
+      <c r="AI5" s="36" t="s">
         <v>98</v>
       </c>
-      <c r="AI5" s="36" t="s">
+      <c r="AJ5" s="36" t="s">
         <v>120</v>
       </c>
-      <c r="AJ5" s="36" t="s">
+      <c r="AK5" s="36" t="s">
         <v>99</v>
       </c>
-      <c r="AK5" s="45" t="s">
+      <c r="AL5" s="45" t="s">
         <v>117</v>
       </c>
-      <c r="AL5" s="45" t="s">
+      <c r="AM5" s="45" t="s">
         <v>118</v>
       </c>
-      <c r="AM5" s="45" t="s">
+      <c r="AN5" s="45" t="s">
         <v>121</v>
       </c>
-      <c r="AN5" s="45" t="s">
+      <c r="AO5" s="45" t="s">
         <v>122</v>
       </c>
-      <c r="AO5" s="36" t="s">
+      <c r="AP5" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="AP5" s="36" t="s">
+      <c r="AQ5" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="AQ5" s="36" t="s">
+      <c r="AR5" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="AR5" s="36" t="s">
+      <c r="AS5" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="AS5" s="36" t="s">
+      <c r="AT5" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="AT5" s="36" t="s">
+      <c r="AU5" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="AU5" s="36" t="s">
+      <c r="AV5" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="AV5" s="36" t="s">
+      <c r="AW5" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="AW5" s="36" t="s">
+      <c r="AX5" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="AX5" s="36" t="s">
+      <c r="AY5" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="AY5" s="36" t="s">
+      <c r="AZ5" s="36" t="s">
         <v>183</v>
       </c>
-      <c r="AZ5" s="36" t="s">
+      <c r="BA5" s="36" t="s">
         <v>186</v>
       </c>
-      <c r="BA5" s="36" t="s">
+      <c r="BB5" s="36" t="s">
         <v>126</v>
       </c>
-      <c r="BB5" s="39" t="s">
+      <c r="BC5" s="39" t="s">
         <v>188</v>
       </c>
-      <c r="BC5" s="39" t="s">
+      <c r="BD5" s="39" t="s">
         <v>190</v>
       </c>
-      <c r="BD5" s="39" t="s">
+      <c r="BE5" s="39" t="s">
         <v>193</v>
       </c>
-      <c r="BE5" s="39" t="s">
+      <c r="BF5" s="39" t="s">
         <v>197</v>
       </c>
-      <c r="BF5" s="39" t="s">
+      <c r="BG5" s="39" t="s">
         <v>199</v>
       </c>
-      <c r="BG5" s="39" t="s">
+      <c r="BH5" s="39" t="s">
         <v>200</v>
       </c>
-      <c r="BH5" s="39" t="s">
+      <c r="BI5" s="39" t="s">
         <v>204</v>
       </c>
-      <c r="BI5" s="39" t="s">
+      <c r="BJ5" s="39" t="s">
         <v>206</v>
       </c>
-      <c r="BJ5" s="39" t="s">
+      <c r="BK5" s="39" t="s">
         <v>207</v>
       </c>
-      <c r="BK5" s="39" t="s">
+      <c r="BL5" s="39" t="s">
         <v>209</v>
       </c>
-      <c r="BL5" s="39" t="s">
+      <c r="BM5" s="39" t="s">
         <v>221</v>
       </c>
-      <c r="BM5" s="39" t="s">
+      <c r="BN5" s="39" t="s">
         <v>222</v>
       </c>
-      <c r="BN5" s="39" t="s">
+      <c r="BO5" s="39" t="s">
         <v>211</v>
       </c>
-      <c r="BO5" s="39" t="s">
+      <c r="BP5" s="39" t="s">
         <v>213</v>
       </c>
-      <c r="BP5" s="39" t="s">
+      <c r="BQ5" s="39" t="s">
         <v>218</v>
       </c>
-      <c r="BQ5" s="39" t="s">
+      <c r="BR5" s="39" t="s">
         <v>215</v>
       </c>
-      <c r="BR5" s="39" t="s">
+      <c r="BS5" s="39" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="11" spans="1:70" x14ac:dyDescent="0.2">
-      <c r="BK11" s="41"/>
-    </row>
-    <row r="12" spans="1:70" x14ac:dyDescent="0.2">
-      <c r="BK12" s="41"/>
-    </row>
-    <row r="13" spans="1:70" x14ac:dyDescent="0.2">
-      <c r="BK13" s="41"/>
-    </row>
-    <row r="14" spans="1:70" x14ac:dyDescent="0.2">
-      <c r="BK14" s="41"/>
+    <row r="11" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="BL11" s="41"/>
+    </row>
+    <row r="12" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="BL12" s="41"/>
+    </row>
+    <row r="13" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="BL13" s="41"/>
+    </row>
+    <row r="14" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="BL14" s="41"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
@@ -44795,70 +44828,73 @@
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A3:C3"/>
   </mergeCells>
-  <dataValidations count="22">
-    <dataValidation showInputMessage="1" showErrorMessage="1" errorTitle="Unknown sex " error="You have entered an unknown value for sex " promptTitle="Sex" sqref="L5" xr:uid="{61B800F7-85EA-B74C-8D79-217EB2BB8728}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI993:AI9991 AJ6:AJ992" xr:uid="{E08CD4DA-AE11-DB40-922E-0C3ECAF74329}">
+  <dataValidations count="23">
+    <dataValidation showInputMessage="1" showErrorMessage="1" errorTitle="Unknown sex " error="You have entered an unknown value for sex " promptTitle="Sex" sqref="M5" xr:uid="{61B800F7-85EA-B74C-8D79-217EB2BB8728}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ993:AJ9991 AK6:AK992" xr:uid="{E08CD4DA-AE11-DB40-922E-0C3ECAF74329}">
       <formula1>"Joules/g"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V993:V9992" xr:uid="{E2A68CBD-EDB8-0D48-9B6E-B29E20DC1B19}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W993:W9992" xr:uid="{E2A68CBD-EDB8-0D48-9B6E-B29E20DC1B19}">
       <formula1>"belly flap, blood, carcass, cleithra, eye lens, fin, gonad, liver, muscle, otolith, scale, spine, stomach, viscera, whole body, whole body (gonads removed), whole body (stomach removed)"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6:F991" xr:uid="{DF355696-A0A3-6D45-A97F-2A26E0345658}">
       <formula1>"spring, summer, fall, winter"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N6:N991" xr:uid="{D59253B5-564B-1D47-923E-DC586A575C35}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O6:O991" xr:uid="{D59253B5-564B-1D47-923E-DC586A575C35}">
       <formula1>"wild, lab"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W6:W991" xr:uid="{618BEA16-FB85-144A-9DB4-305EFF123E53}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X6:X991" xr:uid="{618BEA16-FB85-144A-9DB4-305EFF123E53}">
       <formula1>"wet, dried"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH6:AH991" xr:uid="{66E4A2BE-9678-EC4D-BD77-D6B9C6555CFA}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI6:AI991" xr:uid="{66E4A2BE-9678-EC4D-BD77-D6B9C6555CFA}">
       <formula1>"wet, dry"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE6:AE992" xr:uid="{9917EF8E-9D15-EA4E-B86B-60B39CF888A1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF6:AF992" xr:uid="{9917EF8E-9D15-EA4E-B86B-60B39CF888A1}">
       <formula1>"Parr oxygen bomb, Parr semi-micro oxygen bomb, Phillipson microbomb, Gentry-Weigert bomb, Unknown bomb, Proximate composition, Organic analysis, Wet digestion, Unknown"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BC6:BC9992" xr:uid="{6BCDA29E-00AD-DC44-9456-909A8798CD81}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BD6:BD9992" xr:uid="{6BCDA29E-00AD-DC44-9456-909A8798CD81}">
       <formula1>"% sample weight, % total lipids"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BG6:BG9992" xr:uid="{8DA5F666-C5FB-A546-AA7B-E8D1C34FC070}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH6:BH9992" xr:uid="{8DA5F666-C5FB-A546-AA7B-E8D1C34FC070}">
       <formula1>"∑SFA (saturated), ∑UFA (unsaturated), ∑MUFA (monounsaturated), ∑PUFA (polyunsaturated), ∑n-3, ∑n-6, 14:0, 16:0, 18:0, 16:1n-7 (POA), 18:1n-9 (OA), 18:3n-3 (ALA), 18:4n-3 (SDA), 18:2n-6 (LIN), 20:4n-6 (ARA), 20:5n-3 (EPA), 22:5n-6 (DPA),22:6n-3 (DHA)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BJ7:BJ9992 BJ6" xr:uid="{2FF93C04-BFBA-A042-839F-6119E2726FB2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BK7:BK9992 BK6" xr:uid="{2FF93C04-BFBA-A042-839F-6119E2726FB2}">
       <formula1>"Alanine, Arginine, Aspartic acid, Cysteine, Cystine, Glutamic acid, Glycine, Histidine, Isoleucine, Leucine, Lysine, Methionine, Phenylalanine, Proline, Serine, Threonine, Tyrosine, Valine"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BL6:BL9992" xr:uid="{73E98200-DF79-B04A-8673-08ACB9A22C3B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BM6:BM9992" xr:uid="{73E98200-DF79-B04A-8673-08ACB9A22C3B}">
       <formula1>"Th (free thiamine), TMP (thiamine monophosphate), TPP (thiamine pyrophosphate), TTh (total thiamine)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V6:V992" xr:uid="{46AB659B-2A50-3441-8038-5315F30CB679}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W6:W992" xr:uid="{46AB659B-2A50-3441-8038-5315F30CB679}">
       <formula1>"belly flap, blood, carcass, cleithra, egg, eye lens, fin, gonad, heart, liver, muscle, otolith, scale, spine, stomach, viscera, whole body, whole body (gonads removed), whole body (stomach removed)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T6:T10000" xr:uid="{51C4B292-4D0C-024D-B22F-A10ACA6AD19D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U6:U10000" xr:uid="{51C4B292-4D0C-024D-B22F-A10ACA6AD19D}">
       <formula1>"Individual, Composite, Mean, SD, Equation"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BO6:BO10000" xr:uid="{7BF0785F-9FED-164D-B36A-ADDD49066DAC}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BP6:BP10000" xr:uid="{7BF0785F-9FED-164D-B36A-ADDD49066DAC}">
       <formula1>" total, methyl "</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AU6:AU10000" xr:uid="{0C3C69BE-9F3E-1B4B-A562-52BCC53E43F8}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV6:AV10000" xr:uid="{0C3C69BE-9F3E-1B4B-A562-52BCC53E43F8}">
       <formula1>"bulk, lipid free "</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M6:M10000" xr:uid="{03B901FA-1F79-BB4E-B6EE-6416D33DFA23}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N6:N10000" xr:uid="{03B901FA-1F79-BB4E-B6EE-6416D33DFA23}">
       <formula1>"fry, larva, nymph, pupa, juvenile, adult "</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L6:L10000" xr:uid="{9EAB778A-B8BD-7744-BE56-7767011FBC78}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M6:M10000" xr:uid="{9EAB778A-B8BD-7744-BE56-7767011FBC78}">
       <formula1>"male, female, unknown, both"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R6:R10000" xr:uid="{6DD9AF48-C9F4-794D-A301-44785649F508}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S6:S10000" xr:uid="{6DD9AF48-C9F4-794D-A301-44785649F508}">
       <formula1>"total, fork, standard, carapace"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BD6:BD10000" xr:uid="{46290ED5-325B-D94E-BEBC-1DC1FB1F703B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BE6:BE10000" xr:uid="{46290ED5-325B-D94E-BEBC-1DC1FB1F703B}">
       <formula1>"fatty acids, phospholipids, sterols, triscylglycerides"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BF6:BF10000" xr:uid="{4197F763-E158-4845-8C47-5F6A3E4B3E70}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BG6:BG10000" xr:uid="{4197F763-E158-4845-8C47-5F6A3E4B3E70}">
       <formula1>"µg/mg sample weight,% total fatty acid"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BI6:BI10000" xr:uid="{D97CB6FC-E274-3949-845D-05F3071BE316}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BJ6:BJ10000" xr:uid="{D97CB6FC-E274-3949-845D-05F3071BE316}">
       <formula1>"µg/mg sample weight, % total protein"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L6:L10000" xr:uid="{8239C302-3A93-4F40-823E-392AA82D302A}">
+      <formula1>"Algae, Amphibian, Fish, Invertebrate, Reptile"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/www/data-entry-template/GLATAR_data_entry_template_v20_long.xlsx
+++ b/www/data-entry-template/GLATAR_data_entry_template_v20_long.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benhlina/Library/CloudStorage/Dropbox/GitHub/GLATAR-App/www/data-entry-template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28E787EC-E7F0-DC42-99F9-0631B339ADB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D0994D6-B65C-5C4C-A10E-1BC8B4F7CF93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="34560" windowHeight="19000" xr2:uid="{DE6F8925-643B-304C-8933-23D4A9123DA3}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="34560" windowHeight="19000" activeTab="3" xr2:uid="{DE6F8925-643B-304C-8933-23D4A9123DA3}"/>
   </bookViews>
   <sheets>
     <sheet name="data_dictionary" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="tbl_samples" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data_dictionary!$A$4:$D$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data_dictionary!$A$4:$D$74</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +47,7 @@
     <author>Ben Hlina</author>
   </authors>
   <commentList>
-    <comment ref="AJ5" authorId="0" shapeId="0" xr:uid="{B4D33EEE-BEDB-B341-9363-9D1C96784118}">
+    <comment ref="AI5" authorId="0" shapeId="0" xr:uid="{B4D33EEE-BEDB-B341-9363-9D1C96784118}">
       <text>
         <r>
           <rPr>
@@ -81,7 +81,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AK5" authorId="0" shapeId="0" xr:uid="{238ED598-C074-2B4E-A8CF-63B7194C3AEA}">
+    <comment ref="AJ5" authorId="0" shapeId="0" xr:uid="{238ED598-C074-2B4E-A8CF-63B7194C3AEA}">
       <text>
         <r>
           <rPr>
@@ -118,7 +118,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="324">
   <si>
     <t>Field Name</t>
   </si>
@@ -1196,18 +1196,6 @@
   <si>
     <t>Convert using the following: Kcal/g - multiple by 4184, Kcal/kg - multiple by 4.184, or Kjoules/g - multiple by 1000</t>
   </si>
-  <si>
-    <t>organism_type</t>
-  </si>
-  <si>
-    <t>as in: Invertebrate; format: character</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The organsim type </t>
-  </si>
-  <si>
-    <t>Algae, Amphibian, Fish, Invertebrate, or  Reptile</t>
-  </si>
 </sst>
 </file>
 
@@ -1896,7 +1884,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCDB0B4B-8041-E244-B061-95D35DE0CD3B}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F92"/>
+  <dimension ref="A1:F91"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" style="1" customWidth="1"/>
@@ -2400,242 +2388,240 @@
       <c r="E32" s="30"/>
       <c r="F32" s="30"/>
     </row>
-    <row r="33" spans="1:6" ht="28" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="B33" s="32" t="s">
-        <v>324</v>
+      <c r="B33" s="30" t="s">
+        <v>7</v>
       </c>
       <c r="C33" s="30" t="s">
-        <v>325</v>
+        <v>264</v>
       </c>
       <c r="D33" s="30" t="s">
-        <v>326</v>
-      </c>
-      <c r="E33" s="33" t="s">
-        <v>327</v>
+        <v>265</v>
+      </c>
+      <c r="E33" s="30" t="s">
+        <v>245</v>
       </c>
       <c r="F33" s="30"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" ht="28" x14ac:dyDescent="0.2">
       <c r="A34" s="30" t="s">
         <v>119</v>
       </c>
       <c r="B34" s="30" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C34" s="30" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D34" s="30" t="s">
-        <v>265</v>
-      </c>
-      <c r="E34" s="30" t="s">
-        <v>245</v>
+        <v>179</v>
+      </c>
+      <c r="E34" s="33" t="s">
+        <v>246</v>
       </c>
       <c r="F34" s="30"/>
     </row>
-    <row r="35" spans="1:6" ht="28" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="B35" s="30" t="s">
-        <v>8</v>
+      <c r="B35" s="32" t="s">
+        <v>13</v>
       </c>
       <c r="C35" s="30" t="s">
-        <v>266</v>
-      </c>
-      <c r="D35" s="30" t="s">
-        <v>179</v>
-      </c>
-      <c r="E35" s="33" t="s">
-        <v>246</v>
+        <v>47</v>
+      </c>
+      <c r="D35" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="E35" s="30" t="s">
+        <v>247</v>
       </c>
       <c r="F35" s="30"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" ht="28" x14ac:dyDescent="0.2">
       <c r="A36" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="B36" s="32" t="s">
-        <v>13</v>
+      <c r="B36" s="30" t="s">
+        <v>156</v>
       </c>
       <c r="C36" s="30" t="s">
-        <v>47</v>
+        <v>267</v>
       </c>
       <c r="D36" s="33" t="s">
-        <v>109</v>
-      </c>
-      <c r="E36" s="30" t="s">
-        <v>247</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="E36" s="30"/>
       <c r="F36" s="30"/>
     </row>
-    <row r="37" spans="1:6" ht="28" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" s="30" t="s">
         <v>119</v>
       </c>
       <c r="B37" s="30" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="C37" s="30" t="s">
-        <v>267</v>
-      </c>
-      <c r="D37" s="33" t="s">
-        <v>268</v>
+        <v>287</v>
+      </c>
+      <c r="D37" s="30" t="s">
+        <v>40</v>
       </c>
       <c r="E37" s="30"/>
       <c r="F37" s="30"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" s="30" t="s">
-        <v>119</v>
+        <v>155</v>
       </c>
       <c r="B38" s="30" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
       <c r="C38" s="30" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D38" s="30" t="s">
-        <v>40</v>
+        <v>180</v>
       </c>
       <c r="E38" s="30"/>
       <c r="F38" s="30"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6" ht="28" x14ac:dyDescent="0.2">
       <c r="A39" s="30" t="s">
         <v>155</v>
       </c>
       <c r="B39" s="30" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C39" s="30" t="s">
-        <v>288</v>
-      </c>
-      <c r="D39" s="30" t="s">
-        <v>180</v>
-      </c>
-      <c r="E39" s="30"/>
+        <v>269</v>
+      </c>
+      <c r="D39" s="33" t="s">
+        <v>270</v>
+      </c>
+      <c r="E39" s="30" t="s">
+        <v>248</v>
+      </c>
       <c r="F39" s="30"/>
     </row>
-    <row r="40" spans="1:6" ht="28" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" s="30" t="s">
-        <v>155</v>
+        <v>119</v>
       </c>
       <c r="B40" s="30" t="s">
-        <v>97</v>
+        <v>171</v>
       </c>
       <c r="C40" s="30" t="s">
-        <v>269</v>
-      </c>
-      <c r="D40" s="33" t="s">
-        <v>270</v>
-      </c>
-      <c r="E40" s="30" t="s">
-        <v>248</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="D40" s="30" t="s">
+        <v>271</v>
+      </c>
+      <c r="E40" s="30"/>
       <c r="F40" s="30"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6" ht="42" x14ac:dyDescent="0.2">
       <c r="A41" s="30" t="s">
         <v>119</v>
       </c>
       <c r="B41" s="30" t="s">
-        <v>171</v>
+        <v>231</v>
       </c>
       <c r="C41" s="30" t="s">
-        <v>289</v>
-      </c>
-      <c r="D41" s="30" t="s">
-        <v>271</v>
-      </c>
-      <c r="E41" s="30"/>
+        <v>233</v>
+      </c>
+      <c r="D41" s="33" t="s">
+        <v>272</v>
+      </c>
+      <c r="E41" s="33" t="s">
+        <v>286</v>
+      </c>
       <c r="F41" s="30"/>
     </row>
-    <row r="42" spans="1:6" ht="42" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" s="30" t="s">
         <v>119</v>
       </c>
       <c r="B42" s="30" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C42" s="30" t="s">
-        <v>233</v>
-      </c>
-      <c r="D42" s="33" t="s">
-        <v>272</v>
-      </c>
-      <c r="E42" s="33" t="s">
-        <v>286</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="D42" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="E42" s="30"/>
       <c r="F42" s="30"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6" ht="84" x14ac:dyDescent="0.2">
       <c r="A43" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="B43" s="30" t="s">
-        <v>232</v>
+      <c r="B43" s="32" t="s">
+        <v>9</v>
       </c>
       <c r="C43" s="30" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D43" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="E43" s="30"/>
+        <v>12</v>
+      </c>
+      <c r="E43" s="33" t="s">
+        <v>249</v>
+      </c>
       <c r="F43" s="30"/>
     </row>
-    <row r="44" spans="1:6" ht="84" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" s="30" t="s">
         <v>119</v>
       </c>
       <c r="B44" s="32" t="s">
-        <v>9</v>
+        <v>62</v>
       </c>
       <c r="C44" s="30" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D44" s="30" t="s">
-        <v>12</v>
-      </c>
-      <c r="E44" s="33" t="s">
-        <v>249</v>
+        <v>273</v>
+      </c>
+      <c r="E44" s="30" t="s">
+        <v>250</v>
       </c>
       <c r="F44" s="30"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="B45" s="32" t="s">
-        <v>62</v>
+        <v>16</v>
+      </c>
+      <c r="B45" s="30" t="s">
+        <v>102</v>
       </c>
       <c r="C45" s="30" t="s">
-        <v>63</v>
+        <v>104</v>
       </c>
       <c r="D45" s="30" t="s">
-        <v>273</v>
-      </c>
-      <c r="E45" s="30" t="s">
-        <v>250</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="E45" s="30"/>
       <c r="F45" s="30"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="B46" s="30" t="s">
-        <v>102</v>
+      <c r="B46" s="32" t="s">
+        <v>17</v>
       </c>
       <c r="C46" s="30" t="s">
-        <v>104</v>
+        <v>48</v>
       </c>
       <c r="D46" s="30" t="s">
-        <v>105</v>
+        <v>26</v>
       </c>
       <c r="E46" s="30"/>
       <c r="F46" s="30"/>
@@ -2644,14 +2630,14 @@
       <c r="A47" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="B47" s="32" t="s">
-        <v>17</v>
+      <c r="B47" s="30" t="s">
+        <v>19</v>
       </c>
       <c r="C47" s="30" t="s">
-        <v>48</v>
+        <v>154</v>
       </c>
       <c r="D47" s="30" t="s">
-        <v>26</v>
+        <v>274</v>
       </c>
       <c r="E47" s="30"/>
       <c r="F47" s="30"/>
@@ -2661,13 +2647,13 @@
         <v>16</v>
       </c>
       <c r="B48" s="30" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C48" s="30" t="s">
-        <v>154</v>
+        <v>52</v>
       </c>
       <c r="D48" s="30" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E48" s="30"/>
       <c r="F48" s="30"/>
@@ -2677,99 +2663,99 @@
         <v>16</v>
       </c>
       <c r="B49" s="30" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C49" s="30" t="s">
-        <v>52</v>
+        <v>138</v>
       </c>
       <c r="D49" s="30" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E49" s="30"/>
       <c r="F49" s="30"/>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:6" ht="70" x14ac:dyDescent="0.2">
       <c r="A50" s="30" t="s">
         <v>16</v>
       </c>
       <c r="B50" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="C50" s="30" t="s">
-        <v>138</v>
-      </c>
-      <c r="D50" s="30" t="s">
-        <v>276</v>
+        <v>22</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="E50" s="30"/>
-      <c r="F50" s="30"/>
+      <c r="F50" s="33" t="s">
+        <v>251</v>
+      </c>
     </row>
     <row r="51" spans="1:6" ht="70" x14ac:dyDescent="0.2">
       <c r="A51" s="30" t="s">
         <v>16</v>
       </c>
       <c r="B51" s="30" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E51" s="30"/>
       <c r="F51" s="33" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="70" x14ac:dyDescent="0.2">
       <c r="A52" s="30" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="B52" s="30" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>152</v>
+        <v>279</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="E52" s="30"/>
-      <c r="F52" s="33" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="70" x14ac:dyDescent="0.2">
+        <v>56</v>
+      </c>
+      <c r="E52" s="33" t="s">
+        <v>253</v>
+      </c>
+      <c r="F52" s="30"/>
+    </row>
+    <row r="53" spans="1:6" ht="28" x14ac:dyDescent="0.2">
       <c r="A53" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="B53" s="30" t="s">
-        <v>55</v>
+      <c r="B53" s="34" t="s">
+        <v>92</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E53" s="33" t="s">
-        <v>253</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="E53" s="30"/>
       <c r="F53" s="30"/>
     </row>
-    <row r="54" spans="1:6" ht="28" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="B54" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>281</v>
+      <c r="B54" s="30" t="s">
+        <v>116</v>
+      </c>
+      <c r="C54" s="30" t="s">
+        <v>141</v>
+      </c>
+      <c r="D54" s="30" t="s">
+        <v>282</v>
       </c>
       <c r="E54" s="30"/>
       <c r="F54" s="30"/>
@@ -2779,101 +2765,101 @@
         <v>27</v>
       </c>
       <c r="B55" s="30" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="C55" s="30" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D55" s="30" t="s">
-        <v>282</v>
-      </c>
-      <c r="E55" s="30"/>
+        <v>100</v>
+      </c>
+      <c r="E55" s="30" t="s">
+        <v>254</v>
+      </c>
       <c r="F55" s="30"/>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:6" ht="42" x14ac:dyDescent="0.2">
       <c r="A56" s="30" t="s">
         <v>27</v>
       </c>
       <c r="B56" s="30" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="C56" s="30" t="s">
-        <v>142</v>
+        <v>290</v>
       </c>
       <c r="D56" s="30" t="s">
-        <v>100</v>
-      </c>
-      <c r="E56" s="30" t="s">
-        <v>254</v>
-      </c>
-      <c r="F56" s="30"/>
-    </row>
-    <row r="57" spans="1:6" ht="42" x14ac:dyDescent="0.2">
+        <v>182</v>
+      </c>
+      <c r="E56" s="30"/>
+      <c r="F56" s="33" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="56" x14ac:dyDescent="0.2">
       <c r="A57" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="B57" s="30" t="s">
-        <v>120</v>
+      <c r="B57" s="35" t="s">
+        <v>99</v>
       </c>
       <c r="C57" s="30" t="s">
-        <v>290</v>
+        <v>148</v>
       </c>
       <c r="D57" s="30" t="s">
-        <v>182</v>
-      </c>
-      <c r="E57" s="30"/>
+        <v>101</v>
+      </c>
+      <c r="E57" s="30" t="s">
+        <v>255</v>
+      </c>
       <c r="F57" s="33" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" ht="56" x14ac:dyDescent="0.2">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="B58" s="35" t="s">
-        <v>99</v>
+      <c r="B58" s="30" t="s">
+        <v>117</v>
       </c>
       <c r="C58" s="30" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D58" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="E58" s="30" t="s">
-        <v>255</v>
-      </c>
-      <c r="F58" s="33" t="s">
-        <v>323</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="E58" s="30"/>
+      <c r="F58" s="30"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" s="30" t="s">
         <v>27</v>
       </c>
       <c r="B59" s="30" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C59" s="30" t="s">
-        <v>143</v>
+        <v>283</v>
       </c>
       <c r="D59" s="30" t="s">
-        <v>123</v>
+        <v>220</v>
       </c>
       <c r="E59" s="30"/>
       <c r="F59" s="30"/>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:6" ht="28" x14ac:dyDescent="0.2">
       <c r="A60" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="B60" s="30" t="s">
-        <v>118</v>
+      <c r="B60" s="35" t="s">
+        <v>121</v>
       </c>
       <c r="C60" s="30" t="s">
-        <v>283</v>
-      </c>
-      <c r="D60" s="30" t="s">
-        <v>220</v>
+        <v>284</v>
+      </c>
+      <c r="D60" s="33" t="s">
+        <v>124</v>
       </c>
       <c r="E60" s="30"/>
       <c r="F60" s="30"/>
@@ -2883,29 +2869,29 @@
         <v>27</v>
       </c>
       <c r="B61" s="35" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C61" s="30" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D61" s="33" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E61" s="30"/>
       <c r="F61" s="30"/>
     </row>
-    <row r="62" spans="1:6" ht="28" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="B62" s="35" t="s">
-        <v>122</v>
+        <v>29</v>
+      </c>
+      <c r="B62" s="30" t="s">
+        <v>28</v>
       </c>
       <c r="C62" s="30" t="s">
-        <v>285</v>
-      </c>
-      <c r="D62" s="33" t="s">
-        <v>125</v>
+        <v>291</v>
+      </c>
+      <c r="D62" s="30" t="s">
+        <v>41</v>
       </c>
       <c r="E62" s="30"/>
       <c r="F62" s="30"/>
@@ -2915,13 +2901,13 @@
         <v>29</v>
       </c>
       <c r="B63" s="30" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C63" s="30" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D63" s="30" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E63" s="30"/>
       <c r="F63" s="30"/>
@@ -2931,13 +2917,13 @@
         <v>29</v>
       </c>
       <c r="B64" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C64" s="30" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D64" s="30" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E64" s="30"/>
       <c r="F64" s="30"/>
@@ -2947,13 +2933,13 @@
         <v>29</v>
       </c>
       <c r="B65" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C65" s="30" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D65" s="30" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E65" s="30"/>
       <c r="F65" s="30"/>
@@ -2963,13 +2949,13 @@
         <v>29</v>
       </c>
       <c r="B66" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C66" s="30" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D66" s="30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E66" s="30"/>
       <c r="F66" s="30"/>
@@ -2979,49 +2965,49 @@
         <v>29</v>
       </c>
       <c r="B67" s="30" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C67" s="30" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="D67" s="30" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E67" s="30"/>
       <c r="F67" s="30"/>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:6" ht="28" x14ac:dyDescent="0.2">
       <c r="A68" s="30" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="B68" s="30" t="s">
-        <v>34</v>
+        <v>181</v>
       </c>
       <c r="C68" s="30" t="s">
-        <v>295</v>
-      </c>
-      <c r="D68" s="30" t="s">
-        <v>46</v>
-      </c>
-      <c r="E68" s="30"/>
+        <v>234</v>
+      </c>
+      <c r="D68" s="33" t="s">
+        <v>235</v>
+      </c>
+      <c r="E68" s="30" t="s">
+        <v>256</v>
+      </c>
       <c r="F68" s="30"/>
     </row>
-    <row r="69" spans="1:6" ht="28" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69" s="30" t="s">
         <v>38</v>
       </c>
       <c r="B69" s="30" t="s">
-        <v>181</v>
+        <v>35</v>
       </c>
       <c r="C69" s="30" t="s">
-        <v>234</v>
-      </c>
-      <c r="D69" s="33" t="s">
-        <v>235</v>
-      </c>
-      <c r="E69" s="30" t="s">
-        <v>256</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="D69" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="E69" s="30"/>
       <c r="F69" s="30"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.2">
@@ -3029,13 +3015,13 @@
         <v>38</v>
       </c>
       <c r="B70" s="30" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C70" s="30" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D70" s="30" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E70" s="30"/>
       <c r="F70" s="30"/>
@@ -3045,13 +3031,13 @@
         <v>38</v>
       </c>
       <c r="B71" s="30" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C71" s="30" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D71" s="30" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E71" s="30"/>
       <c r="F71" s="30"/>
@@ -3061,13 +3047,13 @@
         <v>38</v>
       </c>
       <c r="B72" s="30" t="s">
-        <v>37</v>
+        <v>183</v>
       </c>
       <c r="C72" s="30" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D72" s="30" t="s">
-        <v>51</v>
+        <v>184</v>
       </c>
       <c r="E72" s="30"/>
       <c r="F72" s="30"/>
@@ -3077,13 +3063,13 @@
         <v>38</v>
       </c>
       <c r="B73" s="30" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C73" s="30" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D73" s="30" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E73" s="30"/>
       <c r="F73" s="30"/>
@@ -3093,47 +3079,49 @@
         <v>38</v>
       </c>
       <c r="B74" s="30" t="s">
-        <v>186</v>
+        <v>126</v>
       </c>
       <c r="C74" s="30" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D74" s="30" t="s">
-        <v>185</v>
+        <v>127</v>
       </c>
       <c r="E74" s="30"/>
       <c r="F74" s="30"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75" s="30" t="s">
-        <v>38</v>
+        <v>187</v>
       </c>
       <c r="B75" s="30" t="s">
-        <v>126</v>
+        <v>188</v>
       </c>
       <c r="C75" s="30" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D75" s="30" t="s">
-        <v>127</v>
+        <v>189</v>
       </c>
       <c r="E75" s="30"/>
       <c r="F75" s="30"/>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A76" s="30" t="s">
+    <row r="76" spans="1:6" ht="28" x14ac:dyDescent="0.2">
+      <c r="A76" s="33" t="s">
         <v>187</v>
       </c>
-      <c r="B76" s="30" t="s">
-        <v>188</v>
-      </c>
-      <c r="C76" s="30" t="s">
-        <v>302</v>
-      </c>
-      <c r="D76" s="30" t="s">
-        <v>189</v>
-      </c>
-      <c r="E76" s="30"/>
+      <c r="B76" s="33" t="s">
+        <v>190</v>
+      </c>
+      <c r="C76" s="33" t="s">
+        <v>191</v>
+      </c>
+      <c r="D76" s="33" t="s">
+        <v>192</v>
+      </c>
+      <c r="E76" s="30" t="s">
+        <v>312</v>
+      </c>
       <c r="F76" s="30"/>
     </row>
     <row r="77" spans="1:6" ht="28" x14ac:dyDescent="0.2">
@@ -3141,187 +3129,185 @@
         <v>187</v>
       </c>
       <c r="B77" s="33" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C77" s="33" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D77" s="33" t="s">
-        <v>192</v>
-      </c>
-      <c r="E77" s="30" t="s">
-        <v>312</v>
+        <v>195</v>
+      </c>
+      <c r="E77" s="33" t="s">
+        <v>313</v>
       </c>
       <c r="F77" s="30"/>
     </row>
     <row r="78" spans="1:6" ht="28" x14ac:dyDescent="0.2">
       <c r="A78" s="33" t="s">
-        <v>187</v>
-      </c>
-      <c r="B78" s="33" t="s">
-        <v>193</v>
+        <v>196</v>
+      </c>
+      <c r="B78" s="34" t="s">
+        <v>197</v>
       </c>
       <c r="C78" s="33" t="s">
-        <v>194</v>
+        <v>303</v>
       </c>
       <c r="D78" s="33" t="s">
-        <v>195</v>
-      </c>
-      <c r="E78" s="33" t="s">
-        <v>313</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="E78" s="30"/>
       <c r="F78" s="30"/>
     </row>
-    <row r="79" spans="1:6" ht="28" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:6" ht="42" x14ac:dyDescent="0.2">
       <c r="A79" s="33" t="s">
         <v>196</v>
       </c>
       <c r="B79" s="34" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C79" s="33" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D79" s="33" t="s">
-        <v>198</v>
-      </c>
-      <c r="E79" s="30"/>
+        <v>307</v>
+      </c>
+      <c r="E79" s="30" t="s">
+        <v>314</v>
+      </c>
       <c r="F79" s="30"/>
     </row>
-    <row r="80" spans="1:6" ht="42" x14ac:dyDescent="0.2">
-      <c r="A80" s="33" t="s">
+    <row r="80" spans="1:6" ht="112" x14ac:dyDescent="0.2">
+      <c r="A80" s="30" t="s">
         <v>196</v>
       </c>
-      <c r="B80" s="34" t="s">
-        <v>199</v>
-      </c>
-      <c r="C80" s="33" t="s">
-        <v>306</v>
-      </c>
-      <c r="D80" s="33" t="s">
-        <v>307</v>
-      </c>
-      <c r="E80" s="30" t="s">
-        <v>314</v>
+      <c r="B80" s="35" t="s">
+        <v>200</v>
+      </c>
+      <c r="C80" s="30" t="s">
+        <v>201</v>
+      </c>
+      <c r="D80" s="30" t="s">
+        <v>202</v>
+      </c>
+      <c r="E80" s="33" t="s">
+        <v>315</v>
       </c>
       <c r="F80" s="30"/>
     </row>
-    <row r="81" spans="1:6" ht="112" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81" s="30" t="s">
-        <v>196</v>
-      </c>
-      <c r="B81" s="35" t="s">
-        <v>200</v>
+        <v>203</v>
+      </c>
+      <c r="B81" s="30" t="s">
+        <v>204</v>
       </c>
       <c r="C81" s="30" t="s">
-        <v>201</v>
-      </c>
-      <c r="D81" s="30" t="s">
-        <v>202</v>
-      </c>
-      <c r="E81" s="33" t="s">
-        <v>315</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="D81" s="33" t="s">
+        <v>205</v>
+      </c>
+      <c r="E81" s="30"/>
       <c r="F81" s="30"/>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:6" ht="42" x14ac:dyDescent="0.2">
       <c r="A82" s="30" t="s">
         <v>203</v>
       </c>
       <c r="B82" s="30" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C82" s="30" t="s">
-        <v>230</v>
+        <v>306</v>
       </c>
       <c r="D82" s="33" t="s">
-        <v>205</v>
-      </c>
-      <c r="E82" s="30"/>
+        <v>308</v>
+      </c>
+      <c r="E82" s="30" t="s">
+        <v>317</v>
+      </c>
       <c r="F82" s="30"/>
     </row>
-    <row r="83" spans="1:6" ht="42" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:6" ht="84" x14ac:dyDescent="0.2">
       <c r="A83" s="30" t="s">
         <v>203</v>
       </c>
       <c r="B83" s="30" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C83" s="30" t="s">
-        <v>306</v>
+        <v>227</v>
       </c>
       <c r="D83" s="33" t="s">
-        <v>308</v>
-      </c>
-      <c r="E83" s="30" t="s">
-        <v>317</v>
+        <v>208</v>
+      </c>
+      <c r="E83" s="33" t="s">
+        <v>316</v>
       </c>
       <c r="F83" s="30"/>
     </row>
-    <row r="84" spans="1:6" ht="84" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84" s="30" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="B84" s="30" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C84" s="30" t="s">
-        <v>227</v>
-      </c>
-      <c r="D84" s="33" t="s">
-        <v>208</v>
-      </c>
-      <c r="E84" s="33" t="s">
-        <v>316</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="D84" s="30" t="s">
+        <v>210</v>
+      </c>
+      <c r="E84" s="33"/>
       <c r="F84" s="30"/>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:6" ht="42" x14ac:dyDescent="0.2">
       <c r="A85" s="30" t="s">
         <v>219</v>
       </c>
-      <c r="B85" s="30" t="s">
-        <v>209</v>
+      <c r="B85" s="40" t="s">
+        <v>221</v>
       </c>
       <c r="C85" s="30" t="s">
-        <v>224</v>
-      </c>
-      <c r="D85" s="30" t="s">
-        <v>210</v>
-      </c>
-      <c r="E85" s="33"/>
+        <v>225</v>
+      </c>
+      <c r="D85" s="33" t="s">
+        <v>223</v>
+      </c>
+      <c r="E85" s="33" t="s">
+        <v>318</v>
+      </c>
       <c r="F85" s="30"/>
     </row>
-    <row r="86" spans="1:6" ht="42" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86" s="30" t="s">
         <v>219</v>
       </c>
       <c r="B86" s="40" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C86" s="30" t="s">
-        <v>225</v>
-      </c>
-      <c r="D86" s="33" t="s">
-        <v>223</v>
-      </c>
-      <c r="E86" s="33" t="s">
-        <v>318</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="D86" s="30" t="s">
+        <v>319</v>
+      </c>
+      <c r="E86" s="30"/>
       <c r="F86" s="30"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87" s="30" t="s">
-        <v>219</v>
-      </c>
-      <c r="B87" s="40" t="s">
-        <v>222</v>
+        <v>217</v>
+      </c>
+      <c r="B87" s="30" t="s">
+        <v>211</v>
       </c>
       <c r="C87" s="30" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D87" s="30" t="s">
-        <v>319</v>
+        <v>212</v>
       </c>
       <c r="E87" s="30"/>
       <c r="F87" s="30"/>
@@ -3331,15 +3317,17 @@
         <v>217</v>
       </c>
       <c r="B88" s="30" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C88" s="30" t="s">
-        <v>228</v>
+        <v>320</v>
       </c>
       <c r="D88" s="30" t="s">
-        <v>212</v>
-      </c>
-      <c r="E88" s="30"/>
+        <v>214</v>
+      </c>
+      <c r="E88" s="30" t="s">
+        <v>321</v>
+      </c>
       <c r="F88" s="30"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.2">
@@ -3347,17 +3335,15 @@
         <v>217</v>
       </c>
       <c r="B89" s="30" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C89" s="30" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="D89" s="30" t="s">
-        <v>214</v>
-      </c>
-      <c r="E89" s="30" t="s">
-        <v>321</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="E89" s="30"/>
       <c r="F89" s="30"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.2">
@@ -3365,13 +3351,13 @@
         <v>217</v>
       </c>
       <c r="B90" s="30" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C90" s="30" t="s">
-        <v>304</v>
+        <v>229</v>
       </c>
       <c r="D90" s="30" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E90" s="30"/>
       <c r="F90" s="30"/>
@@ -3381,32 +3367,16 @@
         <v>217</v>
       </c>
       <c r="B91" s="30" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C91" s="30" t="s">
-        <v>229</v>
+        <v>305</v>
       </c>
       <c r="D91" s="30" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E91" s="30"/>
       <c r="F91" s="30"/>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A92" s="30" t="s">
-        <v>217</v>
-      </c>
-      <c r="B92" s="30" t="s">
-        <v>216</v>
-      </c>
-      <c r="C92" s="30" t="s">
-        <v>305</v>
-      </c>
-      <c r="D92" s="30" t="s">
-        <v>311</v>
-      </c>
-      <c r="E92" s="30"/>
-      <c r="F92" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -44473,7 +44443,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED99CF4A-5D49-794D-A1CB-3B08F37AF445}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:BS14"/>
+  <dimension ref="A1:BR14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20.5" customWidth="1"/>
@@ -44484,46 +44454,46 @@
     <col min="7" max="7" width="22.5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="26.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="13" customWidth="1"/>
-    <col min="13" max="13" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.1640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9" style="8" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.5" style="8" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="15.5" customWidth="1"/>
-    <col min="29" max="29" width="10.83203125" customWidth="1"/>
-    <col min="30" max="30" width="22.6640625" customWidth="1"/>
-    <col min="31" max="31" width="31.1640625" customWidth="1"/>
-    <col min="32" max="32" width="17.5" customWidth="1"/>
-    <col min="33" max="33" width="27" customWidth="1"/>
-    <col min="34" max="34" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="18.1640625" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="43" max="46" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="21.5" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="13" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="21.83203125" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="63" max="64" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="14.33203125" customWidth="1"/>
-    <col min="66" max="66" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="13" customWidth="1"/>
+    <col min="12" max="12" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9" style="8" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.5" customWidth="1"/>
+    <col min="28" max="28" width="10.83203125" customWidth="1"/>
+    <col min="29" max="29" width="22.6640625" customWidth="1"/>
+    <col min="30" max="30" width="31.1640625" customWidth="1"/>
+    <col min="31" max="31" width="17.5" customWidth="1"/>
+    <col min="32" max="32" width="27" customWidth="1"/>
+    <col min="33" max="33" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="42" max="45" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="21.5" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="13" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="21.83203125" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="62" max="63" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="14.33203125" customWidth="1"/>
+    <col min="65" max="65" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="16.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:71" ht="19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:70" ht="19" x14ac:dyDescent="0.25">
       <c r="A1" s="50" t="s">
         <v>159</v>
       </c>
@@ -44533,7 +44503,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="2" spans="1:71" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:70" x14ac:dyDescent="0.2">
       <c r="A2" s="50" t="s">
         <v>24</v>
       </c>
@@ -44541,7 +44511,7 @@
       <c r="C2" s="51"/>
       <c r="D2" s="6"/>
     </row>
-    <row r="3" spans="1:71" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:70" x14ac:dyDescent="0.2">
       <c r="A3" s="50"/>
       <c r="B3" s="51"/>
       <c r="C3" s="51"/>
@@ -44549,51 +44519,51 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:71" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:70" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>119</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="X4" t="s">
         <v>16</v>
       </c>
-      <c r="AF4" t="s">
+      <c r="AE4" t="s">
         <v>27</v>
       </c>
-      <c r="AP4" t="s">
+      <c r="AO4" t="s">
         <v>29</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AU4" t="s">
         <v>38</v>
       </c>
-      <c r="BC4" s="37" t="s">
+      <c r="BB4" s="37" t="s">
         <v>187</v>
       </c>
+      <c r="BC4" s="37"/>
       <c r="BD4" s="37"/>
-      <c r="BE4" s="37"/>
-      <c r="BF4" s="37" t="s">
+      <c r="BE4" s="37" t="s">
         <v>196</v>
       </c>
+      <c r="BF4" s="37"/>
       <c r="BG4" s="37"/>
-      <c r="BH4" s="37"/>
-      <c r="BI4" s="37" t="s">
+      <c r="BH4" s="37" t="s">
         <v>203</v>
       </c>
+      <c r="BI4" s="38"/>
       <c r="BJ4" s="38"/>
-      <c r="BK4" s="38"/>
-      <c r="BL4" s="38" t="s">
+      <c r="BK4" s="38" t="s">
         <v>219</v>
       </c>
+      <c r="BL4" s="38"/>
       <c r="BM4" s="38"/>
-      <c r="BN4" s="38"/>
-      <c r="BO4" s="38" t="s">
+      <c r="BN4" s="38" t="s">
         <v>217</v>
       </c>
+      <c r="BO4" s="38"/>
       <c r="BP4" s="38"/>
       <c r="BQ4" s="38"/>
       <c r="BR4" s="38"/>
-      <c r="BS4" s="38"/>
-    </row>
-    <row r="5" spans="1:71" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:70" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="42" t="s">
         <v>14</v>
       </c>
@@ -44628,197 +44598,194 @@
         <v>103</v>
       </c>
       <c r="L5" s="36" t="s">
-        <v>324</v>
+        <v>166</v>
       </c>
       <c r="M5" s="36" t="s">
-        <v>166</v>
-      </c>
-      <c r="N5" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="O5" s="44" t="s">
+      <c r="N5" s="44" t="s">
         <v>13</v>
       </c>
+      <c r="O5" s="36" t="s">
+        <v>156</v>
+      </c>
       <c r="P5" s="36" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="Q5" s="36" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
       <c r="R5" s="36" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="S5" s="36" t="s">
-        <v>97</v>
-      </c>
-      <c r="T5" s="36" t="s">
         <v>171</v>
       </c>
-      <c r="U5" s="46" t="s">
+      <c r="T5" s="46" t="s">
         <v>231</v>
       </c>
-      <c r="V5" s="45" t="s">
+      <c r="U5" s="45" t="s">
         <v>232</v>
       </c>
-      <c r="W5" s="44" t="s">
+      <c r="V5" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="X5" s="46" t="s">
+      <c r="W5" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="Y5" s="45" t="s">
+      <c r="X5" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="Z5" s="44" t="s">
+      <c r="Y5" s="44" t="s">
         <v>17</v>
       </c>
+      <c r="Z5" s="36" t="s">
+        <v>19</v>
+      </c>
       <c r="AA5" s="36" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AB5" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="AC5" s="36" t="s">
         <v>21</v>
       </c>
+      <c r="AC5" s="47" t="s">
+        <v>167</v>
+      </c>
       <c r="AD5" s="47" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AE5" s="47" t="s">
-        <v>168</v>
+        <v>55</v>
       </c>
       <c r="AF5" s="47" t="s">
-        <v>55</v>
-      </c>
-      <c r="AG5" s="47" t="s">
         <v>92</v>
       </c>
+      <c r="AG5" s="36" t="s">
+        <v>116</v>
+      </c>
       <c r="AH5" s="36" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="AI5" s="36" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="AJ5" s="36" t="s">
-        <v>120</v>
-      </c>
-      <c r="AK5" s="36" t="s">
         <v>99</v>
       </c>
+      <c r="AK5" s="45" t="s">
+        <v>117</v>
+      </c>
       <c r="AL5" s="45" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AM5" s="45" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AN5" s="45" t="s">
-        <v>121</v>
-      </c>
-      <c r="AO5" s="45" t="s">
         <v>122</v>
       </c>
+      <c r="AO5" s="36" t="s">
+        <v>28</v>
+      </c>
       <c r="AP5" s="36" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AQ5" s="36" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AR5" s="36" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AS5" s="36" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AT5" s="36" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AU5" s="36" t="s">
-        <v>34</v>
+        <v>181</v>
       </c>
       <c r="AV5" s="36" t="s">
-        <v>181</v>
+        <v>35</v>
       </c>
       <c r="AW5" s="36" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AX5" s="36" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AY5" s="36" t="s">
-        <v>37</v>
+        <v>183</v>
       </c>
       <c r="AZ5" s="36" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="BA5" s="36" t="s">
-        <v>186</v>
-      </c>
-      <c r="BB5" s="36" t="s">
         <v>126</v>
       </c>
+      <c r="BB5" s="39" t="s">
+        <v>188</v>
+      </c>
       <c r="BC5" s="39" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="BD5" s="39" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="BE5" s="39" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="BF5" s="39" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="BG5" s="39" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="BH5" s="39" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="BI5" s="39" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="BJ5" s="39" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="BK5" s="39" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="BL5" s="39" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="BM5" s="39" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="BN5" s="39" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="BO5" s="39" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="BP5" s="39" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="BQ5" s="39" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="BR5" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="BS5" s="39" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="11" spans="1:71" x14ac:dyDescent="0.2">
-      <c r="BL11" s="41"/>
-    </row>
-    <row r="12" spans="1:71" x14ac:dyDescent="0.2">
-      <c r="BL12" s="41"/>
-    </row>
-    <row r="13" spans="1:71" x14ac:dyDescent="0.2">
-      <c r="BL13" s="41"/>
-    </row>
-    <row r="14" spans="1:71" x14ac:dyDescent="0.2">
-      <c r="BL14" s="41"/>
+    <row r="11" spans="1:70" x14ac:dyDescent="0.2">
+      <c r="BK11" s="41"/>
+    </row>
+    <row r="12" spans="1:70" x14ac:dyDescent="0.2">
+      <c r="BK12" s="41"/>
+    </row>
+    <row r="13" spans="1:70" x14ac:dyDescent="0.2">
+      <c r="BK13" s="41"/>
+    </row>
+    <row r="14" spans="1:70" x14ac:dyDescent="0.2">
+      <c r="BK14" s="41"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
@@ -44828,73 +44795,70 @@
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A3:C3"/>
   </mergeCells>
-  <dataValidations count="23">
-    <dataValidation showInputMessage="1" showErrorMessage="1" errorTitle="Unknown sex " error="You have entered an unknown value for sex " promptTitle="Sex" sqref="M5" xr:uid="{61B800F7-85EA-B74C-8D79-217EB2BB8728}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ993:AJ9991 AK6:AK992" xr:uid="{E08CD4DA-AE11-DB40-922E-0C3ECAF74329}">
+  <dataValidations count="22">
+    <dataValidation showInputMessage="1" showErrorMessage="1" errorTitle="Unknown sex " error="You have entered an unknown value for sex " promptTitle="Sex" sqref="L5" xr:uid="{61B800F7-85EA-B74C-8D79-217EB2BB8728}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI993:AI9991 AJ6:AJ992" xr:uid="{E08CD4DA-AE11-DB40-922E-0C3ECAF74329}">
       <formula1>"Joules/g"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W993:W9992" xr:uid="{E2A68CBD-EDB8-0D48-9B6E-B29E20DC1B19}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V993:V9992" xr:uid="{E2A68CBD-EDB8-0D48-9B6E-B29E20DC1B19}">
       <formula1>"belly flap, blood, carcass, cleithra, eye lens, fin, gonad, liver, muscle, otolith, scale, spine, stomach, viscera, whole body, whole body (gonads removed), whole body (stomach removed)"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6:F991" xr:uid="{DF355696-A0A3-6D45-A97F-2A26E0345658}">
       <formula1>"spring, summer, fall, winter"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O6:O991" xr:uid="{D59253B5-564B-1D47-923E-DC586A575C35}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N6:N991" xr:uid="{D59253B5-564B-1D47-923E-DC586A575C35}">
       <formula1>"wild, lab"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X6:X991" xr:uid="{618BEA16-FB85-144A-9DB4-305EFF123E53}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W6:W991" xr:uid="{618BEA16-FB85-144A-9DB4-305EFF123E53}">
       <formula1>"wet, dried"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI6:AI991" xr:uid="{66E4A2BE-9678-EC4D-BD77-D6B9C6555CFA}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH6:AH991" xr:uid="{66E4A2BE-9678-EC4D-BD77-D6B9C6555CFA}">
       <formula1>"wet, dry"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF6:AF992" xr:uid="{9917EF8E-9D15-EA4E-B86B-60B39CF888A1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE6:AE992" xr:uid="{9917EF8E-9D15-EA4E-B86B-60B39CF888A1}">
       <formula1>"Parr oxygen bomb, Parr semi-micro oxygen bomb, Phillipson microbomb, Gentry-Weigert bomb, Unknown bomb, Proximate composition, Organic analysis, Wet digestion, Unknown"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BD6:BD9992" xr:uid="{6BCDA29E-00AD-DC44-9456-909A8798CD81}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BC6:BC9992" xr:uid="{6BCDA29E-00AD-DC44-9456-909A8798CD81}">
       <formula1>"% sample weight, % total lipids"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH6:BH9992" xr:uid="{8DA5F666-C5FB-A546-AA7B-E8D1C34FC070}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BG6:BG9992" xr:uid="{8DA5F666-C5FB-A546-AA7B-E8D1C34FC070}">
       <formula1>"∑SFA (saturated), ∑UFA (unsaturated), ∑MUFA (monounsaturated), ∑PUFA (polyunsaturated), ∑n-3, ∑n-6, 14:0, 16:0, 18:0, 16:1n-7 (POA), 18:1n-9 (OA), 18:3n-3 (ALA), 18:4n-3 (SDA), 18:2n-6 (LIN), 20:4n-6 (ARA), 20:5n-3 (EPA), 22:5n-6 (DPA),22:6n-3 (DHA)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BK7:BK9992 BK6" xr:uid="{2FF93C04-BFBA-A042-839F-6119E2726FB2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BJ7:BJ9992 BJ6" xr:uid="{2FF93C04-BFBA-A042-839F-6119E2726FB2}">
       <formula1>"Alanine, Arginine, Aspartic acid, Cysteine, Cystine, Glutamic acid, Glycine, Histidine, Isoleucine, Leucine, Lysine, Methionine, Phenylalanine, Proline, Serine, Threonine, Tyrosine, Valine"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BM6:BM9992" xr:uid="{73E98200-DF79-B04A-8673-08ACB9A22C3B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BL6:BL9992" xr:uid="{73E98200-DF79-B04A-8673-08ACB9A22C3B}">
       <formula1>"Th (free thiamine), TMP (thiamine monophosphate), TPP (thiamine pyrophosphate), TTh (total thiamine)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W6:W992" xr:uid="{46AB659B-2A50-3441-8038-5315F30CB679}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V6:V992" xr:uid="{46AB659B-2A50-3441-8038-5315F30CB679}">
       <formula1>"belly flap, blood, carcass, cleithra, egg, eye lens, fin, gonad, heart, liver, muscle, otolith, scale, spine, stomach, viscera, whole body, whole body (gonads removed), whole body (stomach removed)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U6:U10000" xr:uid="{51C4B292-4D0C-024D-B22F-A10ACA6AD19D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T6:T10000" xr:uid="{51C4B292-4D0C-024D-B22F-A10ACA6AD19D}">
       <formula1>"Individual, Composite, Mean, SD, Equation"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BP6:BP10000" xr:uid="{7BF0785F-9FED-164D-B36A-ADDD49066DAC}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BO6:BO10000" xr:uid="{7BF0785F-9FED-164D-B36A-ADDD49066DAC}">
       <formula1>" total, methyl "</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV6:AV10000" xr:uid="{0C3C69BE-9F3E-1B4B-A562-52BCC53E43F8}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AU6:AU10000" xr:uid="{0C3C69BE-9F3E-1B4B-A562-52BCC53E43F8}">
       <formula1>"bulk, lipid free "</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N6:N10000" xr:uid="{03B901FA-1F79-BB4E-B6EE-6416D33DFA23}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M6:M10000" xr:uid="{03B901FA-1F79-BB4E-B6EE-6416D33DFA23}">
       <formula1>"fry, larva, nymph, pupa, juvenile, adult "</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M6:M10000" xr:uid="{9EAB778A-B8BD-7744-BE56-7767011FBC78}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L6:L10000" xr:uid="{9EAB778A-B8BD-7744-BE56-7767011FBC78}">
       <formula1>"male, female, unknown, both"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S6:S10000" xr:uid="{6DD9AF48-C9F4-794D-A301-44785649F508}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R6:R10000" xr:uid="{6DD9AF48-C9F4-794D-A301-44785649F508}">
       <formula1>"total, fork, standard, carapace"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BE6:BE10000" xr:uid="{46290ED5-325B-D94E-BEBC-1DC1FB1F703B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BD6:BD10000" xr:uid="{46290ED5-325B-D94E-BEBC-1DC1FB1F703B}">
       <formula1>"fatty acids, phospholipids, sterols, triscylglycerides"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BG6:BG10000" xr:uid="{4197F763-E158-4845-8C47-5F6A3E4B3E70}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BF6:BF10000" xr:uid="{4197F763-E158-4845-8C47-5F6A3E4B3E70}">
       <formula1>"µg/mg sample weight,% total fatty acid"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BJ6:BJ10000" xr:uid="{D97CB6FC-E274-3949-845D-05F3071BE316}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BI6:BI10000" xr:uid="{D97CB6FC-E274-3949-845D-05F3071BE316}">
       <formula1>"µg/mg sample weight, % total protein"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L6:L10000" xr:uid="{8239C302-3A93-4F40-823E-392AA82D302A}">
-      <formula1>"Algae, Amphibian, Fish, Invertebrate, Reptile"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/www/data-entry-template/GLATAR_data_entry_template_v20_long.xlsx
+++ b/www/data-entry-template/GLATAR_data_entry_template_v20_long.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benhlina/Library/CloudStorage/Dropbox/GitHub/GLATAR-App/www/data-entry-template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D0994D6-B65C-5C4C-A10E-1BC8B4F7CF93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B89DCA5F-083B-BB48-81C0-3336CF5BBF1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="34560" windowHeight="19000" activeTab="3" xr2:uid="{DE6F8925-643B-304C-8933-23D4A9123DA3}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="34560" windowHeight="19000" xr2:uid="{DE6F8925-643B-304C-8933-23D4A9123DA3}"/>
   </bookViews>
   <sheets>
     <sheet name="data_dictionary" sheetId="1" r:id="rId1"/>
@@ -1026,9 +1026,6 @@
     <t>as in: juvenile; format: character</t>
   </si>
   <si>
-    <t>as in: control: format: character</t>
-  </si>
-  <si>
     <t>For lab studies, what was the treatment (e.g., control, diet #2, or T22degC)</t>
   </si>
   <si>
@@ -1122,9 +1119,6 @@
     <t xml:space="preserve">as in: 8.34 ‰; format: numeric; place to 2 decimals </t>
   </si>
   <si>
-    <t>as in: -14.50 ‰; format:numeric; places to 2 decimals</t>
-  </si>
-  <si>
     <t>as in: -150.40 ‰; numeric: integer; places to 2 decimals</t>
   </si>
   <si>
@@ -1195,6 +1189,12 @@
   </si>
   <si>
     <t>Convert using the following: Kcal/g - multiple by 4184, Kcal/kg - multiple by 4.184, or Kjoules/g - multiple by 1000</t>
+  </si>
+  <si>
+    <t>as in: control; format: character</t>
+  </si>
+  <si>
+    <t>as in: -14.50 ‰; format: numeric; places to 2 decimals</t>
   </si>
 </sst>
 </file>
@@ -1536,13 +1536,13 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1897,20 +1897,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="51" t="s">
         <v>238</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
     </row>
     <row r="2" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="51" t="s">
         <v>162</v>
       </c>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="21" t="s">
@@ -2450,10 +2450,10 @@
         <v>156</v>
       </c>
       <c r="C36" s="30" t="s">
+        <v>322</v>
+      </c>
+      <c r="D36" s="33" t="s">
         <v>267</v>
-      </c>
-      <c r="D36" s="33" t="s">
-        <v>268</v>
       </c>
       <c r="E36" s="30"/>
       <c r="F36" s="30"/>
@@ -2466,7 +2466,7 @@
         <v>170</v>
       </c>
       <c r="C37" s="30" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D37" s="30" t="s">
         <v>40</v>
@@ -2482,7 +2482,7 @@
         <v>96</v>
       </c>
       <c r="C38" s="30" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D38" s="30" t="s">
         <v>180</v>
@@ -2498,10 +2498,10 @@
         <v>97</v>
       </c>
       <c r="C39" s="30" t="s">
+        <v>268</v>
+      </c>
+      <c r="D39" s="33" t="s">
         <v>269</v>
-      </c>
-      <c r="D39" s="33" t="s">
-        <v>270</v>
       </c>
       <c r="E39" s="30" t="s">
         <v>248</v>
@@ -2516,10 +2516,10 @@
         <v>171</v>
       </c>
       <c r="C40" s="30" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D40" s="30" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E40" s="30"/>
       <c r="F40" s="30"/>
@@ -2535,10 +2535,10 @@
         <v>233</v>
       </c>
       <c r="D41" s="33" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E41" s="33" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F41" s="30"/>
     </row>
@@ -2587,7 +2587,7 @@
         <v>63</v>
       </c>
       <c r="D44" s="30" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E44" s="30" t="s">
         <v>250</v>
@@ -2637,7 +2637,7 @@
         <v>154</v>
       </c>
       <c r="D47" s="30" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E47" s="30"/>
       <c r="F47" s="30"/>
@@ -2653,7 +2653,7 @@
         <v>52</v>
       </c>
       <c r="D48" s="30" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E48" s="30"/>
       <c r="F48" s="30"/>
@@ -2669,7 +2669,7 @@
         <v>138</v>
       </c>
       <c r="D49" s="30" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E49" s="30"/>
       <c r="F49" s="30"/>
@@ -2685,7 +2685,7 @@
         <v>151</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E50" s="30"/>
       <c r="F50" s="33" t="s">
@@ -2703,7 +2703,7 @@
         <v>152</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E51" s="30"/>
       <c r="F51" s="33" t="s">
@@ -2718,7 +2718,7 @@
         <v>55</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>56</v>
@@ -2736,10 +2736,10 @@
         <v>92</v>
       </c>
       <c r="C53" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="D53" s="3" t="s">
         <v>280</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>281</v>
       </c>
       <c r="E53" s="30"/>
       <c r="F53" s="30"/>
@@ -2755,7 +2755,7 @@
         <v>141</v>
       </c>
       <c r="D54" s="30" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E54" s="30"/>
       <c r="F54" s="30"/>
@@ -2786,14 +2786,14 @@
         <v>120</v>
       </c>
       <c r="C56" s="30" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D56" s="30" t="s">
         <v>182</v>
       </c>
       <c r="E56" s="30"/>
       <c r="F56" s="33" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="56" x14ac:dyDescent="0.2">
@@ -2813,7 +2813,7 @@
         <v>255</v>
       </c>
       <c r="F57" s="33" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
@@ -2840,7 +2840,7 @@
         <v>118</v>
       </c>
       <c r="C59" s="30" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D59" s="30" t="s">
         <v>220</v>
@@ -2856,7 +2856,7 @@
         <v>121</v>
       </c>
       <c r="C60" s="30" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D60" s="33" t="s">
         <v>124</v>
@@ -2872,7 +2872,7 @@
         <v>122</v>
       </c>
       <c r="C61" s="30" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D61" s="33" t="s">
         <v>125</v>
@@ -2888,7 +2888,7 @@
         <v>28</v>
       </c>
       <c r="C62" s="30" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D62" s="30" t="s">
         <v>41</v>
@@ -2904,7 +2904,7 @@
         <v>30</v>
       </c>
       <c r="C63" s="30" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D63" s="30" t="s">
         <v>42</v>
@@ -2920,7 +2920,7 @@
         <v>31</v>
       </c>
       <c r="C64" s="30" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D64" s="30" t="s">
         <v>43</v>
@@ -2936,7 +2936,7 @@
         <v>32</v>
       </c>
       <c r="C65" s="30" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D65" s="30" t="s">
         <v>44</v>
@@ -2952,7 +2952,7 @@
         <v>33</v>
       </c>
       <c r="C66" s="30" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D66" s="30" t="s">
         <v>45</v>
@@ -2968,7 +2968,7 @@
         <v>34</v>
       </c>
       <c r="C67" s="30" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D67" s="30" t="s">
         <v>46</v>
@@ -3002,7 +3002,7 @@
         <v>35</v>
       </c>
       <c r="C69" s="30" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D69" s="30" t="s">
         <v>49</v>
@@ -3018,7 +3018,7 @@
         <v>36</v>
       </c>
       <c r="C70" s="30" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D70" s="30" t="s">
         <v>50</v>
@@ -3034,7 +3034,7 @@
         <v>37</v>
       </c>
       <c r="C71" s="30" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D71" s="30" t="s">
         <v>51</v>
@@ -3050,7 +3050,7 @@
         <v>183</v>
       </c>
       <c r="C72" s="30" t="s">
-        <v>299</v>
+        <v>323</v>
       </c>
       <c r="D72" s="30" t="s">
         <v>184</v>
@@ -3066,7 +3066,7 @@
         <v>186</v>
       </c>
       <c r="C73" s="30" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D73" s="30" t="s">
         <v>185</v>
@@ -3082,7 +3082,7 @@
         <v>126</v>
       </c>
       <c r="C74" s="30" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D74" s="30" t="s">
         <v>127</v>
@@ -3098,7 +3098,7 @@
         <v>188</v>
       </c>
       <c r="C75" s="30" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D75" s="30" t="s">
         <v>189</v>
@@ -3120,7 +3120,7 @@
         <v>192</v>
       </c>
       <c r="E76" s="30" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F76" s="30"/>
     </row>
@@ -3138,7 +3138,7 @@
         <v>195</v>
       </c>
       <c r="E77" s="33" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F77" s="30"/>
     </row>
@@ -3150,7 +3150,7 @@
         <v>197</v>
       </c>
       <c r="C78" s="33" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D78" s="33" t="s">
         <v>198</v>
@@ -3166,13 +3166,13 @@
         <v>199</v>
       </c>
       <c r="C79" s="33" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D79" s="33" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="E79" s="30" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F79" s="30"/>
     </row>
@@ -3190,7 +3190,7 @@
         <v>202</v>
       </c>
       <c r="E80" s="33" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="F80" s="30"/>
     </row>
@@ -3218,13 +3218,13 @@
         <v>206</v>
       </c>
       <c r="C82" s="30" t="s">
+        <v>304</v>
+      </c>
+      <c r="D82" s="33" t="s">
         <v>306</v>
       </c>
-      <c r="D82" s="33" t="s">
-        <v>308</v>
-      </c>
       <c r="E82" s="30" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F82" s="30"/>
     </row>
@@ -3242,7 +3242,7 @@
         <v>208</v>
       </c>
       <c r="E83" s="33" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F83" s="30"/>
     </row>
@@ -3276,7 +3276,7 @@
         <v>223</v>
       </c>
       <c r="E85" s="33" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F85" s="30"/>
     </row>
@@ -3291,7 +3291,7 @@
         <v>226</v>
       </c>
       <c r="D86" s="30" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E86" s="30"/>
       <c r="F86" s="30"/>
@@ -3320,13 +3320,13 @@
         <v>213</v>
       </c>
       <c r="C88" s="30" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D88" s="30" t="s">
         <v>214</v>
       </c>
       <c r="E88" s="30" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="F88" s="30"/>
     </row>
@@ -3338,10 +3338,10 @@
         <v>218</v>
       </c>
       <c r="C89" s="30" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D89" s="30" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E89" s="30"/>
       <c r="F89" s="30"/>
@@ -3357,7 +3357,7 @@
         <v>229</v>
       </c>
       <c r="D90" s="30" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E90" s="30"/>
       <c r="F90" s="30"/>
@@ -3370,10 +3370,10 @@
         <v>216</v>
       </c>
       <c r="C91" s="30" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D91" s="30" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E91" s="30"/>
       <c r="F91" s="30"/>
@@ -3399,27 +3399,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="19" x14ac:dyDescent="0.25">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="49" t="s">
         <v>172</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
       <c r="D1" s="10" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="49" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
       <c r="D2" s="11"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="50"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
+      <c r="A3" s="49"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
       <c r="D3" s="11" t="s">
         <v>176</v>
       </c>
@@ -3465,27 +3465,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="19" x14ac:dyDescent="0.25">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="49" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
       <c r="D1" s="10" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="49" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
       <c r="D2" s="11"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A3" s="50"/>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
+      <c r="A3" s="49"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="50"/>
       <c r="D3" s="11" t="s">
         <v>25</v>
       </c>
@@ -44494,27 +44494,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:70" ht="19" x14ac:dyDescent="0.25">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="49" t="s">
         <v>159</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
       <c r="D1" s="5" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="2" spans="1:70" x14ac:dyDescent="0.2">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="49" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
       <c r="D2" s="6"/>
     </row>
     <row r="3" spans="1:70" x14ac:dyDescent="0.2">
-      <c r="A3" s="50"/>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
+      <c r="A3" s="49"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="50"/>
       <c r="D3" s="6" t="s">
         <v>25</v>
       </c>

--- a/www/data-entry-template/GLATAR_data_entry_template_v20_long.xlsx
+++ b/www/data-entry-template/GLATAR_data_entry_template_v20_long.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benhlina/Library/CloudStorage/Dropbox/GitHub/GLATAR-App/www/data-entry-template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B89DCA5F-083B-BB48-81C0-3336CF5BBF1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D62A128-4E4E-6D4B-86A2-959B6980142B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="34560" windowHeight="19000" xr2:uid="{DE6F8925-643B-304C-8933-23D4A9123DA3}"/>
   </bookViews>
@@ -118,7 +118,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="325">
   <si>
     <t>Field Name</t>
   </si>
@@ -957,9 +957,6 @@
     <t xml:space="preserve">If unpublished please put unpublished as the title </t>
   </si>
   <si>
-    <t>If there is no common name for a speices, genus, family ect. then use the scientific name (e.g., Diporia spp.)</t>
-  </si>
-  <si>
     <t>male, female, unknown, or both</t>
   </si>
   <si>
@@ -1195,6 +1192,12 @@
   </si>
   <si>
     <t>as in: -14.50 ‰; format: numeric; places to 2 decimals</t>
+  </si>
+  <si>
+    <t>If there is no common name for a speices, genus, family ect. then use the scientific name (e.g., Diporia spp.); If validation does not return a valid common name and you have searched the taxonomic table but haven't found the species; please contact the database manager</t>
+  </si>
+  <si>
+    <t>If there is no genus and species for the organism then use the next type of classifcation e.g., family ect. (Salvelinus); If validation does not return a valid scientific name and you have searched the taxonomic table but haven't found the species; please contact the database manager</t>
   </si>
 </sst>
 </file>
@@ -1536,13 +1539,13 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1897,20 +1900,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="49" t="s">
         <v>238</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
     </row>
     <row r="2" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="49" t="s">
         <v>162</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="21" t="s">
@@ -1943,7 +1946,7 @@
         <v>178</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E5" s="30"/>
       <c r="F5" s="30"/>
@@ -1959,7 +1962,7 @@
         <v>157</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E6" s="30"/>
       <c r="F6" s="30"/>
@@ -1975,7 +1978,7 @@
         <v>144</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E7" s="30"/>
       <c r="F7" s="30"/>
@@ -1991,7 +1994,7 @@
         <v>54</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E8" s="30"/>
       <c r="F8" s="30"/>
@@ -2041,7 +2044,7 @@
         <v>144</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E11" s="30"/>
       <c r="F11" s="30"/>
@@ -2322,7 +2325,7 @@
       <c r="E28" s="30"/>
       <c r="F28" s="30"/>
     </row>
-    <row r="29" spans="1:6" ht="56" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" ht="126" x14ac:dyDescent="0.2">
       <c r="A29" s="30" t="s">
         <v>119</v>
       </c>
@@ -2330,17 +2333,17 @@
         <v>6</v>
       </c>
       <c r="C29" s="30" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D29" s="30" t="s">
         <v>11</v>
       </c>
       <c r="E29" s="30"/>
       <c r="F29" s="33" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="140" x14ac:dyDescent="0.2">
       <c r="A30" s="30" t="s">
         <v>119</v>
       </c>
@@ -2351,10 +2354,12 @@
         <v>135</v>
       </c>
       <c r="D30" s="30" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E30" s="30"/>
-      <c r="F30" s="30"/>
+      <c r="F30" s="33" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="30" t="s">
@@ -2396,13 +2401,13 @@
         <v>7</v>
       </c>
       <c r="C33" s="30" t="s">
+        <v>263</v>
+      </c>
+      <c r="D33" s="30" t="s">
         <v>264</v>
       </c>
-      <c r="D33" s="30" t="s">
-        <v>265</v>
-      </c>
       <c r="E33" s="30" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F33" s="30"/>
     </row>
@@ -2414,13 +2419,13 @@
         <v>8</v>
       </c>
       <c r="C34" s="30" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D34" s="30" t="s">
         <v>179</v>
       </c>
       <c r="E34" s="33" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F34" s="30"/>
     </row>
@@ -2438,7 +2443,7 @@
         <v>109</v>
       </c>
       <c r="E35" s="30" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F35" s="30"/>
     </row>
@@ -2450,10 +2455,10 @@
         <v>156</v>
       </c>
       <c r="C36" s="30" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D36" s="33" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E36" s="30"/>
       <c r="F36" s="30"/>
@@ -2466,7 +2471,7 @@
         <v>170</v>
       </c>
       <c r="C37" s="30" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D37" s="30" t="s">
         <v>40</v>
@@ -2482,7 +2487,7 @@
         <v>96</v>
       </c>
       <c r="C38" s="30" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D38" s="30" t="s">
         <v>180</v>
@@ -2498,13 +2503,13 @@
         <v>97</v>
       </c>
       <c r="C39" s="30" t="s">
+        <v>267</v>
+      </c>
+      <c r="D39" s="33" t="s">
         <v>268</v>
       </c>
-      <c r="D39" s="33" t="s">
-        <v>269</v>
-      </c>
       <c r="E39" s="30" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F39" s="30"/>
     </row>
@@ -2516,10 +2521,10 @@
         <v>171</v>
       </c>
       <c r="C40" s="30" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D40" s="30" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E40" s="30"/>
       <c r="F40" s="30"/>
@@ -2535,10 +2540,10 @@
         <v>233</v>
       </c>
       <c r="D41" s="33" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E41" s="33" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F41" s="30"/>
     </row>
@@ -2572,7 +2577,7 @@
         <v>12</v>
       </c>
       <c r="E43" s="33" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F43" s="30"/>
     </row>
@@ -2587,43 +2592,45 @@
         <v>63</v>
       </c>
       <c r="D44" s="30" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E44" s="30" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F44" s="30"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" s="30" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="B45" s="30" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="C45" s="30" t="s">
-        <v>104</v>
+        <v>141</v>
       </c>
       <c r="D45" s="30" t="s">
-        <v>105</v>
+        <v>280</v>
       </c>
       <c r="E45" s="30"/>
       <c r="F45" s="30"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="B46" s="32" t="s">
-        <v>17</v>
+        <v>27</v>
+      </c>
+      <c r="B46" s="30" t="s">
+        <v>98</v>
       </c>
       <c r="C46" s="30" t="s">
-        <v>48</v>
+        <v>142</v>
       </c>
       <c r="D46" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="E46" s="30"/>
+        <v>100</v>
+      </c>
+      <c r="E46" s="30" t="s">
+        <v>253</v>
+      </c>
       <c r="F46" s="30"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
@@ -2631,13 +2638,13 @@
         <v>16</v>
       </c>
       <c r="B47" s="30" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="C47" s="30" t="s">
-        <v>154</v>
+        <v>104</v>
       </c>
       <c r="D47" s="30" t="s">
-        <v>273</v>
+        <v>105</v>
       </c>
       <c r="E47" s="30"/>
       <c r="F47" s="30"/>
@@ -2646,14 +2653,14 @@
       <c r="A48" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="B48" s="30" t="s">
-        <v>20</v>
+      <c r="B48" s="32" t="s">
+        <v>17</v>
       </c>
       <c r="C48" s="30" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D48" s="30" t="s">
-        <v>274</v>
+        <v>26</v>
       </c>
       <c r="E48" s="30"/>
       <c r="F48" s="30"/>
@@ -2663,119 +2670,117 @@
         <v>16</v>
       </c>
       <c r="B49" s="30" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C49" s="30" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="D49" s="30" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="E49" s="30"/>
       <c r="F49" s="30"/>
     </row>
-    <row r="50" spans="1:6" ht="70" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" s="30" t="s">
         <v>16</v>
       </c>
       <c r="B50" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>276</v>
+        <v>20</v>
+      </c>
+      <c r="C50" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="D50" s="30" t="s">
+        <v>273</v>
       </c>
       <c r="E50" s="30"/>
-      <c r="F50" s="33" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="70" x14ac:dyDescent="0.2">
+      <c r="F50" s="30"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" s="30" t="s">
         <v>16</v>
       </c>
       <c r="B51" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>277</v>
+        <v>21</v>
+      </c>
+      <c r="C51" s="30" t="s">
+        <v>138</v>
+      </c>
+      <c r="D51" s="30" t="s">
+        <v>274</v>
       </c>
       <c r="E51" s="30"/>
-      <c r="F51" s="33" t="s">
-        <v>252</v>
-      </c>
+      <c r="F51" s="30"/>
     </row>
     <row r="52" spans="1:6" ht="70" x14ac:dyDescent="0.2">
       <c r="A52" s="30" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B52" s="30" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>278</v>
+        <v>151</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E52" s="33" t="s">
-        <v>253</v>
-      </c>
-      <c r="F52" s="30"/>
-    </row>
-    <row r="53" spans="1:6" ht="28" x14ac:dyDescent="0.2">
+        <v>275</v>
+      </c>
+      <c r="E52" s="30"/>
+      <c r="F52" s="33" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="70" x14ac:dyDescent="0.2">
       <c r="A53" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="B53" s="34" t="s">
-        <v>92</v>
+        <v>16</v>
+      </c>
+      <c r="B53" s="30" t="s">
+        <v>23</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>279</v>
+        <v>152</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="E53" s="30"/>
-      <c r="F53" s="30"/>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F53" s="33" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="70" x14ac:dyDescent="0.2">
       <c r="A54" s="30" t="s">
         <v>27</v>
       </c>
       <c r="B54" s="30" t="s">
-        <v>116</v>
-      </c>
-      <c r="C54" s="30" t="s">
-        <v>141</v>
-      </c>
-      <c r="D54" s="30" t="s">
-        <v>281</v>
-      </c>
-      <c r="E54" s="30"/>
+        <v>55</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E54" s="33" t="s">
+        <v>252</v>
+      </c>
       <c r="F54" s="30"/>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:6" ht="28" x14ac:dyDescent="0.2">
       <c r="A55" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="B55" s="30" t="s">
-        <v>98</v>
-      </c>
-      <c r="C55" s="30" t="s">
-        <v>142</v>
-      </c>
-      <c r="D55" s="30" t="s">
-        <v>100</v>
-      </c>
-      <c r="E55" s="30" t="s">
-        <v>254</v>
-      </c>
+      <c r="B55" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="E55" s="30"/>
       <c r="F55" s="30"/>
     </row>
     <row r="56" spans="1:6" ht="42" x14ac:dyDescent="0.2">
@@ -2786,14 +2791,14 @@
         <v>120</v>
       </c>
       <c r="C56" s="30" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D56" s="30" t="s">
         <v>182</v>
       </c>
       <c r="E56" s="30"/>
       <c r="F56" s="33" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="56" x14ac:dyDescent="0.2">
@@ -2810,10 +2815,10 @@
         <v>101</v>
       </c>
       <c r="E57" s="30" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F57" s="33" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
@@ -2840,7 +2845,7 @@
         <v>118</v>
       </c>
       <c r="C59" s="30" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D59" s="30" t="s">
         <v>220</v>
@@ -2856,7 +2861,7 @@
         <v>121</v>
       </c>
       <c r="C60" s="30" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D60" s="33" t="s">
         <v>124</v>
@@ -2872,7 +2877,7 @@
         <v>122</v>
       </c>
       <c r="C61" s="30" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D61" s="33" t="s">
         <v>125</v>
@@ -2888,7 +2893,7 @@
         <v>28</v>
       </c>
       <c r="C62" s="30" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D62" s="30" t="s">
         <v>41</v>
@@ -2904,7 +2909,7 @@
         <v>30</v>
       </c>
       <c r="C63" s="30" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D63" s="30" t="s">
         <v>42</v>
@@ -2920,7 +2925,7 @@
         <v>31</v>
       </c>
       <c r="C64" s="30" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D64" s="30" t="s">
         <v>43</v>
@@ -2936,7 +2941,7 @@
         <v>32</v>
       </c>
       <c r="C65" s="30" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D65" s="30" t="s">
         <v>44</v>
@@ -2952,7 +2957,7 @@
         <v>33</v>
       </c>
       <c r="C66" s="30" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D66" s="30" t="s">
         <v>45</v>
@@ -2968,7 +2973,7 @@
         <v>34</v>
       </c>
       <c r="C67" s="30" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D67" s="30" t="s">
         <v>46</v>
@@ -2990,7 +2995,7 @@
         <v>235</v>
       </c>
       <c r="E68" s="30" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F68" s="30"/>
     </row>
@@ -3002,7 +3007,7 @@
         <v>35</v>
       </c>
       <c r="C69" s="30" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D69" s="30" t="s">
         <v>49</v>
@@ -3018,7 +3023,7 @@
         <v>36</v>
       </c>
       <c r="C70" s="30" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D70" s="30" t="s">
         <v>50</v>
@@ -3034,7 +3039,7 @@
         <v>37</v>
       </c>
       <c r="C71" s="30" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D71" s="30" t="s">
         <v>51</v>
@@ -3050,7 +3055,7 @@
         <v>183</v>
       </c>
       <c r="C72" s="30" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D72" s="30" t="s">
         <v>184</v>
@@ -3066,7 +3071,7 @@
         <v>186</v>
       </c>
       <c r="C73" s="30" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D73" s="30" t="s">
         <v>185</v>
@@ -3082,7 +3087,7 @@
         <v>126</v>
       </c>
       <c r="C74" s="30" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D74" s="30" t="s">
         <v>127</v>
@@ -3098,7 +3103,7 @@
         <v>188</v>
       </c>
       <c r="C75" s="30" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D75" s="30" t="s">
         <v>189</v>
@@ -3120,7 +3125,7 @@
         <v>192</v>
       </c>
       <c r="E76" s="30" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F76" s="30"/>
     </row>
@@ -3138,7 +3143,7 @@
         <v>195</v>
       </c>
       <c r="E77" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F77" s="30"/>
     </row>
@@ -3150,7 +3155,7 @@
         <v>197</v>
       </c>
       <c r="C78" s="33" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D78" s="33" t="s">
         <v>198</v>
@@ -3166,13 +3171,13 @@
         <v>199</v>
       </c>
       <c r="C79" s="33" t="s">
+        <v>303</v>
+      </c>
+      <c r="D79" s="33" t="s">
         <v>304</v>
       </c>
-      <c r="D79" s="33" t="s">
-        <v>305</v>
-      </c>
       <c r="E79" s="30" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F79" s="30"/>
     </row>
@@ -3190,7 +3195,7 @@
         <v>202</v>
       </c>
       <c r="E80" s="33" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F80" s="30"/>
     </row>
@@ -3218,13 +3223,13 @@
         <v>206</v>
       </c>
       <c r="C82" s="30" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D82" s="33" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E82" s="30" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F82" s="30"/>
     </row>
@@ -3242,7 +3247,7 @@
         <v>208</v>
       </c>
       <c r="E83" s="33" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F83" s="30"/>
     </row>
@@ -3276,7 +3281,7 @@
         <v>223</v>
       </c>
       <c r="E85" s="33" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F85" s="30"/>
     </row>
@@ -3291,7 +3296,7 @@
         <v>226</v>
       </c>
       <c r="D86" s="30" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E86" s="30"/>
       <c r="F86" s="30"/>
@@ -3320,13 +3325,13 @@
         <v>213</v>
       </c>
       <c r="C88" s="30" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D88" s="30" t="s">
         <v>214</v>
       </c>
       <c r="E88" s="30" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F88" s="30"/>
     </row>
@@ -3338,10 +3343,10 @@
         <v>218</v>
       </c>
       <c r="C89" s="30" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D89" s="30" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E89" s="30"/>
       <c r="F89" s="30"/>
@@ -3357,7 +3362,7 @@
         <v>229</v>
       </c>
       <c r="D90" s="30" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E90" s="30"/>
       <c r="F90" s="30"/>
@@ -3370,10 +3375,10 @@
         <v>216</v>
       </c>
       <c r="C91" s="30" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D91" s="30" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E91" s="30"/>
       <c r="F91" s="30"/>
@@ -3399,27 +3404,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="19" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="50" t="s">
         <v>172</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
       <c r="D1" s="10" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
       <c r="D2" s="11"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="49"/>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
+      <c r="A3" s="50"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="50"/>
       <c r="D3" s="11" t="s">
         <v>176</v>
       </c>
@@ -3465,27 +3470,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="19" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="50" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
       <c r="D1" s="10" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
       <c r="D2" s="11"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A3" s="49"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
+      <c r="A3" s="50"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="51"/>
       <c r="D3" s="11" t="s">
         <v>25</v>
       </c>
@@ -44462,14 +44467,14 @@
     <col min="21" max="21" width="11" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="15.5" style="8" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="15.5" customWidth="1"/>
-    <col min="28" max="28" width="10.83203125" customWidth="1"/>
-    <col min="29" max="29" width="22.6640625" customWidth="1"/>
-    <col min="30" max="30" width="31.1640625" customWidth="1"/>
-    <col min="31" max="31" width="17.5" customWidth="1"/>
-    <col min="32" max="32" width="27" customWidth="1"/>
-    <col min="33" max="33" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15.5" customWidth="1"/>
+    <col min="30" max="30" width="10.83203125" customWidth="1"/>
+    <col min="31" max="31" width="22.6640625" customWidth="1"/>
+    <col min="32" max="32" width="31.1640625" customWidth="1"/>
+    <col min="33" max="33" width="17.5" customWidth="1"/>
+    <col min="34" max="34" width="27" customWidth="1"/>
     <col min="35" max="35" width="18.1640625" bestFit="1" customWidth="1"/>
     <col min="41" max="41" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="42" max="45" width="13.33203125" bestFit="1" customWidth="1"/>
@@ -44494,27 +44499,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:70" ht="19" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="50" t="s">
         <v>159</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
       <c r="D1" s="5" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="2" spans="1:70" x14ac:dyDescent="0.2">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
       <c r="D2" s="6"/>
     </row>
     <row r="3" spans="1:70" x14ac:dyDescent="0.2">
-      <c r="A3" s="49"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
+      <c r="A3" s="50"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="51"/>
       <c r="D3" s="6" t="s">
         <v>25</v>
       </c>
@@ -44523,10 +44528,10 @@
       <c r="A4" t="s">
         <v>119</v>
       </c>
-      <c r="X4" t="s">
+      <c r="Z4" t="s">
         <v>16</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AG4" t="s">
         <v>27</v>
       </c>
       <c r="AO4" t="s">
@@ -44633,38 +44638,38 @@
       <c r="W5" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="X5" s="45" t="s">
+      <c r="X5" s="36" t="s">
+        <v>116</v>
+      </c>
+      <c r="Y5" s="36" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z5" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="Y5" s="44" t="s">
+      <c r="AA5" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="Z5" s="36" t="s">
+      <c r="AB5" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="AA5" s="36" t="s">
+      <c r="AC5" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="AB5" s="36" t="s">
+      <c r="AD5" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="AC5" s="47" t="s">
+      <c r="AE5" s="47" t="s">
         <v>167</v>
       </c>
-      <c r="AD5" s="47" t="s">
+      <c r="AF5" s="47" t="s">
         <v>168</v>
       </c>
-      <c r="AE5" s="47" t="s">
+      <c r="AG5" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="AF5" s="47" t="s">
+      <c r="AH5" s="47" t="s">
         <v>92</v>
-      </c>
-      <c r="AG5" s="36" t="s">
-        <v>116</v>
-      </c>
-      <c r="AH5" s="36" t="s">
-        <v>98</v>
       </c>
       <c r="AI5" s="36" t="s">
         <v>120</v>
@@ -44812,10 +44817,10 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W6:W991" xr:uid="{618BEA16-FB85-144A-9DB4-305EFF123E53}">
       <formula1>"wet, dried"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH6:AH991" xr:uid="{66E4A2BE-9678-EC4D-BD77-D6B9C6555CFA}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y6:Y991" xr:uid="{66E4A2BE-9678-EC4D-BD77-D6B9C6555CFA}">
       <formula1>"wet, dry"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE6:AE992" xr:uid="{9917EF8E-9D15-EA4E-B86B-60B39CF888A1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG6:AG992" xr:uid="{9917EF8E-9D15-EA4E-B86B-60B39CF888A1}">
       <formula1>"Parr oxygen bomb, Parr semi-micro oxygen bomb, Phillipson microbomb, Gentry-Weigert bomb, Unknown bomb, Proximate composition, Organic analysis, Wet digestion, Unknown"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BC6:BC9992" xr:uid="{6BCDA29E-00AD-DC44-9456-909A8798CD81}">
@@ -44824,7 +44829,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BG6:BG9992" xr:uid="{8DA5F666-C5FB-A546-AA7B-E8D1C34FC070}">
       <formula1>"∑SFA (saturated), ∑UFA (unsaturated), ∑MUFA (monounsaturated), ∑PUFA (polyunsaturated), ∑n-3, ∑n-6, 14:0, 16:0, 18:0, 16:1n-7 (POA), 18:1n-9 (OA), 18:3n-3 (ALA), 18:4n-3 (SDA), 18:2n-6 (LIN), 20:4n-6 (ARA), 20:5n-3 (EPA), 22:5n-6 (DPA),22:6n-3 (DHA)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BJ7:BJ9992 BJ6" xr:uid="{2FF93C04-BFBA-A042-839F-6119E2726FB2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BJ6:BJ9992" xr:uid="{2FF93C04-BFBA-A042-839F-6119E2726FB2}">
       <formula1>"Alanine, Arginine, Aspartic acid, Cysteine, Cystine, Glutamic acid, Glycine, Histidine, Isoleucine, Leucine, Lysine, Methionine, Phenylalanine, Proline, Serine, Threonine, Tyrosine, Valine"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BL6:BL9992" xr:uid="{73E98200-DF79-B04A-8673-08ACB9A22C3B}">
